--- a/Farm Soils Data.xlsx
+++ b/Farm Soils Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://princetonu-my.sharepoint.com/personal/cg3403_princeton_edu/Documents/Undergraduate Research/Thesis Files/Thesis Rmd Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1147" documentId="11_F25DC773A252ABDACC1048EB41DB448A5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE5CCEA6-D7B5-460D-A573-858F1F2598D6}"/>
+  <xr:revisionPtr revIDLastSave="1835" documentId="11_F25DC773A252ABDACC1048EB41DB448A5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D002BF18-488B-4409-8D9A-9FE48655C303}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="884" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,10 @@
     <sheet name="Characterization" sheetId="1" r:id="rId1"/>
     <sheet name="Oven Drying &amp; Combustion" sheetId="2" r:id="rId2"/>
     <sheet name="Trial Metadata" sheetId="7" r:id="rId3"/>
-    <sheet name="Soil Sample Management" sheetId="6" r:id="rId4"/>
-    <sheet name="01-28-26 Soy-UD" sheetId="5" r:id="rId5"/>
+    <sheet name="Soil Samples for Rutgers" sheetId="8" r:id="rId4"/>
+    <sheet name="Soil Sample Management" sheetId="6" r:id="rId5"/>
     <sheet name="H Calibration" sheetId="4" r:id="rId6"/>
+    <sheet name="incomplete 01-28-26 Soy-UD" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="202">
   <si>
     <t>Soybean Undisturbed</t>
   </si>
@@ -49,12 +50,6 @@
     <t>Soybean Center</t>
   </si>
   <si>
-    <t>Rosemary</t>
-  </si>
-  <si>
-    <t>Oregano</t>
-  </si>
-  <si>
     <t>Mass Grad Cyl + Soil</t>
   </si>
   <si>
@@ -145,12 +140,6 @@
     <t>Avg. Mass g Water/Mass g Air Dry Soil</t>
   </si>
   <si>
-    <t>Proportion OM per g dehydrated Soil</t>
-  </si>
-  <si>
-    <t>Concentration</t>
-  </si>
-  <si>
     <t>H2 Area</t>
   </si>
   <si>
@@ -268,9 +257,6 @@
     <t>CG,QQ,EO</t>
   </si>
   <si>
-    <t>CG. EO</t>
-  </si>
-  <si>
     <t>CG,XZ,FP,EO</t>
   </si>
   <si>
@@ -395,6 +381,273 @@
   </si>
   <si>
     <t>soil_type</t>
+  </si>
+  <si>
+    <t>Range H2</t>
+  </si>
+  <si>
+    <t>RF H2</t>
+  </si>
+  <si>
+    <t>CG,EO</t>
+  </si>
+  <si>
+    <t>Concentration (ppm)</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-15-1</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-15-2</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-15-3</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-25-1</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-25-2</t>
+  </si>
+  <si>
+    <t>Short-Soy-UD-25-3</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-15-1</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-15-2</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-15-3</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-25-1</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-25-2</t>
+  </si>
+  <si>
+    <t>Short-Soy-C-25-3</t>
+  </si>
+  <si>
+    <t>Crack before start</t>
+  </si>
+  <si>
+    <t>Broken Rim</t>
+  </si>
+  <si>
+    <t>Location Coords</t>
+  </si>
+  <si>
+    <t>No Crack I don't think…</t>
+  </si>
+  <si>
+    <t>Bottle Broke at End, glass in saturation can maybe?</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>FGF-ROX-1 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-ORX-1 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-YBW-1 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-SUN-1 6-23-25</t>
+  </si>
+  <si>
+    <t>MOF-CH-1 7-19-25</t>
+  </si>
+  <si>
+    <t>MOF-AS-1 7-19-25</t>
+  </si>
+  <si>
+    <t>FGF-OR-1 10-17-25</t>
+  </si>
+  <si>
+    <t>FGF-RO-1 10-17-25</t>
+  </si>
+  <si>
+    <t>FGF-OSUN-1 10-17-25</t>
+  </si>
+  <si>
+    <t>FGF-FBW-1 10-17-25</t>
+  </si>
+  <si>
+    <t>SOY-C-1 10-24-25</t>
+  </si>
+  <si>
+    <t>SOY-UD-1 10-24-25</t>
+  </si>
+  <si>
+    <t>FGF-SUN-2 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-SOD-1 10-17-25</t>
+  </si>
+  <si>
+    <t>FGF-YBW-2 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-CO-1 10-17-25</t>
+  </si>
+  <si>
+    <t>FGF-YC-1 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-SODX-1 6-23-25</t>
+  </si>
+  <si>
+    <t>FGF-OR-15-1</t>
+  </si>
+  <si>
+    <t>FGF-OR-15-2</t>
+  </si>
+  <si>
+    <t>FGF-OR-15-3</t>
+  </si>
+  <si>
+    <t>FGF-OR-25-1</t>
+  </si>
+  <si>
+    <t>FGF-OR-25-2</t>
+  </si>
+  <si>
+    <t>FGF-OR-25-3</t>
+  </si>
+  <si>
+    <t>FGF Rosemary</t>
+  </si>
+  <si>
+    <t>FGF Oregano</t>
+  </si>
+  <si>
+    <t>FGF Sod</t>
+  </si>
+  <si>
+    <t>FGF Sunflower</t>
+  </si>
+  <si>
+    <t>FGF Corn</t>
+  </si>
+  <si>
+    <t>FGF Buckwheat</t>
+  </si>
+  <si>
+    <t>FGF-RO-15-1</t>
+  </si>
+  <si>
+    <t>FGF-RO-15-2</t>
+  </si>
+  <si>
+    <t>FGF-RO-15-3</t>
+  </si>
+  <si>
+    <t>FGF-RO-25-1</t>
+  </si>
+  <si>
+    <t>FGF-RO-25-2</t>
+  </si>
+  <si>
+    <t>FGF-RO-25-3</t>
+  </si>
+  <si>
+    <t>Cracked Bottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNTESTED BELOW </t>
+  </si>
+  <si>
+    <t>Percent OM per g dehydrated Soil</t>
+  </si>
+  <si>
+    <t>WPA maybe -8.45? Forgor</t>
+  </si>
+  <si>
+    <t>SO SLOW</t>
+  </si>
+  <si>
+    <t>FGF-SOD-15-1</t>
+  </si>
+  <si>
+    <t>FGF-SOD-15-2</t>
+  </si>
+  <si>
+    <t>FGF-SOD-15-3</t>
+  </si>
+  <si>
+    <t>FGF-SOD-25-1</t>
+  </si>
+  <si>
+    <t>FGF-SOD-25-2</t>
+  </si>
+  <si>
+    <t>FGF-SOD-25-3</t>
+  </si>
+  <si>
+    <t>FGF-CORN-15-1</t>
+  </si>
+  <si>
+    <t>FGF-CORN-15-2</t>
+  </si>
+  <si>
+    <t>FGF-CORN-15-3</t>
+  </si>
+  <si>
+    <t>FGF-CORN-25-1</t>
+  </si>
+  <si>
+    <t>FGF-CORN-25-2</t>
+  </si>
+  <si>
+    <t>FGF-CORN-25-3</t>
+  </si>
+  <si>
+    <t>WP may be wrong, number slipped mind (but I think it was -19.something)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>FGF-FBW-15-1</t>
+  </si>
+  <si>
+    <t>FGF-FBW-15-2</t>
+  </si>
+  <si>
+    <t>FGF-FBW-15-3</t>
+  </si>
+  <si>
+    <t>FGF-FBW-25-1</t>
+  </si>
+  <si>
+    <t>FGF-FBW-25-2</t>
+  </si>
+  <si>
+    <t>FGF-FBW-25-3</t>
+  </si>
+  <si>
+    <t>FGF-SUN-15-1</t>
+  </si>
+  <si>
+    <t>FGF-SUN-15-2</t>
+  </si>
+  <si>
+    <t>FGF-SUN-15-3</t>
+  </si>
+  <si>
+    <t>FGF-SUN-25-1</t>
+  </si>
+  <si>
+    <t>FGF-SUN-25-2</t>
+  </si>
+  <si>
+    <t>FGF-SUN-25-3</t>
   </si>
 </sst>
 </file>
@@ -428,12 +681,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -449,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -462,6 +721,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,6 +741,1066 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Trial Metadata'!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Short-Soy-UD-15-1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Trial Metadata'!$H$14:$H$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>-9.0299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-5.78</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.66</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Trial Metadata'!$M$14:$M$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8.6554098540546853E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10456218218159971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5278024515902462E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19636418157673172</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18604842525895229</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14540502883805442</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8B80-4223-9052-69640CFBEF66}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Trial Metadata'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Short-Soy-C-15-1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Trial Metadata'!$H$20:$H$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>-5.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-11.78</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Trial Metadata'!$M$20:$M$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.11055213004484259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9517848212055879E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10000719493476481</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28234736301597274</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20396043771044287</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14075461776112638</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A7D4-47E0-9FAA-C066169ACF78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="589615615"/>
+        <c:axId val="589618015"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="589615615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589618015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="589618015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589615615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>21896</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4219D6A-FB23-39E1-C868-993A7E93DFAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -767,67 +2090,67 @@
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="P1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -889,11 +2212,11 @@
         <f>AVERAGE('Oven Drying &amp; Combustion'!I2:I4)</f>
         <v>2.0882128689861692E-2</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="9">
         <f>P2*M2/(0.01*O2)</f>
         <v>4.0382824251009468E-2</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="9">
         <f>AVERAGE('Oven Drying &amp; Combustion'!L2:L4)</f>
         <v>8.2879580299641487E-2</v>
       </c>
@@ -902,7 +2225,7 @@
         <v>4.8070156573792058E-2</v>
       </c>
       <c r="T2" s="6">
-        <f>15*$O2*(2*(1-$L2))*(10^-4)/$M2-(2*$L2)</f>
+        <f>(15*$O2*(2*(1-$L2))*(10^-4)/$M2)-(2*$L2)</f>
         <v>0.11104861580595798</v>
       </c>
       <c r="U2" s="6">
@@ -973,11 +2296,11 @@
         <f>AVERAGE('Oven Drying &amp; Combustion'!I5:I7)</f>
         <v>2.1286444450847018E-2</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q5" si="6">P3*M3/(0.01*O3)</f>
         <v>4.9978797700217868E-2</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="9">
         <f>AVERAGE('Oven Drying &amp; Combustion'!L5:L7)</f>
         <v>5.8943500371858783E-2</v>
       </c>
@@ -986,7 +2309,7 @@
         <v>3.4187230215678092E-2</v>
       </c>
       <c r="T3" s="6">
-        <f t="shared" ref="T3:T5" si="8">15*$O3*(2*(1-$L3))*(10^-4)/$M3-(2*$L3)</f>
+        <f t="shared" ref="T3:T9" si="8">(15*$O3*(2*(1-$L3))*(10^-4)/$M3)-(2*$L3)</f>
         <v>8.3424900313693151E-2</v>
       </c>
       <c r="U3" s="6">
@@ -1000,7 +2323,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="B4">
         <v>120.41</v>
@@ -1057,11 +2380,11 @@
         <f>AVERAGE('Oven Drying &amp; Combustion'!I8:I10)</f>
         <v>2.6877913815344396E-2</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="9">
         <f t="shared" si="6"/>
         <v>7.7139612650038436E-2</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="9">
         <f>AVERAGE('Oven Drying &amp; Combustion'!L8:L10)</f>
         <v>7.7033603747011861E-2</v>
       </c>
@@ -1074,7 +2397,7 @@
         <v>4.9445160178720624E-2</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" ref="U4:U5" si="9">25*$O4*(2*(1-$L4))*(10^-4)/$M4-(2*$L4)</f>
+        <f t="shared" ref="U4:U9" si="9">25*$O4*(2*(1-$L4))*(10^-4)/$M4-(2*$L4)</f>
         <v>0.11730758270119482</v>
       </c>
       <c r="V4" s="6">
@@ -1084,7 +2407,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="B5">
         <v>121.46</v>
@@ -1141,11 +2464,11 @@
         <f>AVERAGE('Oven Drying &amp; Combustion'!I11:I13)</f>
         <v>2.1687842348556283E-2</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="9">
         <f t="shared" si="6"/>
         <v>6.5042871957717824E-2</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="9">
         <f>AVERAGE('Oven Drying &amp; Combustion'!L11:L13)</f>
         <v>6.8702090373020733E-2</v>
       </c>
@@ -1167,115 +2490,339 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6">
+        <v>121.47</v>
+      </c>
       <c r="C6">
         <v>50</v>
       </c>
+      <c r="D6">
+        <v>176.61</v>
+      </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>55.140000000000015</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
+      <c r="G6">
+        <v>76</v>
+      </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.1028000000000002</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K6" t="e">
+        <v>2.1207692307692314</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>48</v>
+      </c>
+      <c r="L6" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!H14:H16)</f>
+        <v>2.2813220184722833E-2</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" ref="M6:M9" si="11">I6*(1-$L6)</f>
+        <v>1.0776415807802879</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" ref="N6:N9" si="12">J6*(1-$L6)</f>
+        <v>2.0723876553467075</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" ref="O6:O9" si="13">K6*(1-$L6)</f>
+        <v>46.904965431133306</v>
+      </c>
+      <c r="P6" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!I14:I16)</f>
+        <v>2.3346482594926204E-2</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" ref="Q6:Q9" si="14">P6*M6/(0.01*O6)</f>
+        <v>5.3638543761842968E-2</v>
+      </c>
+      <c r="R6" s="9">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!L14:L16)</f>
+        <v>6.7781429852761907E-2</v>
+      </c>
+      <c r="S6" s="7">
+        <f t="shared" ref="S6:S9" si="15">R6*0.58</f>
+        <v>3.9313229314601905E-2</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" si="8"/>
+        <v>8.1971398126564399E-2</v>
+      </c>
+      <c r="U6" s="6">
+        <f>25*$O6*(2*(1-$L6))*(10^-4)/$M6-(2*$L6)</f>
+        <v>0.1670366237905711</v>
+      </c>
+      <c r="V6" s="6">
+        <f t="shared" ref="V6:V9" si="16">Q6/P6</f>
+        <v>2.2975000000000008</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7">
+        <v>121.01</v>
+      </c>
       <c r="C7">
         <v>50</v>
       </c>
+      <c r="D7">
+        <v>172.31</v>
+      </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="F7">
         <v>50</v>
       </c>
+      <c r="G7">
+        <v>76</v>
+      </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K7" t="e">
+        <v>1.973076923076923</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>47.999999999999993</v>
+      </c>
+      <c r="L7" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!H17:H19)</f>
+        <v>2.8139439781671074E-2</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="11"/>
+        <v>0.99712893478400544</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="12"/>
+        <v>1.9175556438153949</v>
+      </c>
+      <c r="O7" s="3">
+        <f t="shared" si="13"/>
+        <v>46.649306890479778</v>
+      </c>
+      <c r="P7" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!I17:I19)</f>
+        <v>2.8954669032480198E-2</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" si="14"/>
+        <v>6.1890605056926437E-2</v>
+      </c>
+      <c r="R7" s="9">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!L17:L19)</f>
+        <v>0.11499575663204196</v>
+      </c>
+      <c r="S7" s="7">
+        <f t="shared" si="15"/>
+        <v>6.6697538846584331E-2</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="8"/>
+        <v>8.0122602572563623E-2</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="9"/>
+        <v>0.17105692399650083</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="16"/>
+        <v>2.1375000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8">
+        <v>126.95</v>
+      </c>
       <c r="C8">
         <v>50</v>
       </c>
+      <c r="D8">
+        <v>190.3</v>
+      </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>63.350000000000009</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>28</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2670000000000001</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K8" t="e">
+        <v>2.2625000000000002</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>44</v>
+      </c>
+      <c r="L8" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!H20:H22)</f>
+        <v>2.2388381229477543E-2</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="11"/>
+        <v>1.2386339209822521</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="12"/>
+        <v>2.2118462874683074</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" si="13"/>
+        <v>43.014911225902992</v>
+      </c>
+      <c r="P8" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!I20:I22)</f>
+        <v>2.2901165307932209E-2</v>
+      </c>
+      <c r="Q8" s="9">
+        <f t="shared" si="14"/>
+        <v>6.5944946466250251E-2</v>
+      </c>
+      <c r="R8" s="9">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!L20:L22)</f>
+        <v>7.0265409564747972E-2</v>
+      </c>
+      <c r="S8" s="7">
+        <f t="shared" si="15"/>
+        <v>4.0753937547553819E-2</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="8"/>
+        <v>5.707385607120196E-2</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="9"/>
+        <v>0.12497426842463996</v>
+      </c>
+      <c r="V8" s="6">
+        <f t="shared" si="16"/>
+        <v>2.8795454545454549</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9">
+        <v>42.34</v>
+      </c>
       <c r="C9">
         <v>50</v>
       </c>
+      <c r="D9">
+        <v>105.13</v>
+      </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>62.789999999999992</v>
       </c>
       <c r="F9">
         <v>50</v>
       </c>
+      <c r="G9">
+        <v>78</v>
+      </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>28</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2557999999999998</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K9" t="e">
+        <v>2.2424999999999997</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>44</v>
+      </c>
+      <c r="L9" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!H23:H25)</f>
+        <v>2.2857187404085832E-2</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="11"/>
+        <v>1.2270959440579488</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="12"/>
+        <v>2.1912427572463371</v>
+      </c>
+      <c r="O9" s="3">
+        <f t="shared" si="13"/>
+        <v>42.994283754220227</v>
+      </c>
+      <c r="P9" s="2">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!I23:I25)</f>
+        <v>2.3393009270672862E-2</v>
+      </c>
+      <c r="Q9" s="9">
+        <f t="shared" si="14"/>
+        <v>6.6765775095706748E-2</v>
+      </c>
+      <c r="R9" s="9">
+        <f>AVERAGE('Oven Drying &amp; Combustion'!L23:L25)</f>
+        <v>6.8808094361031288E-2</v>
+      </c>
+      <c r="S9" s="7">
+        <f t="shared" si="15"/>
+        <v>3.9908694729398148E-2</v>
+      </c>
+      <c r="T9" s="6">
+        <f t="shared" si="8"/>
+        <v>5.6995333156998514E-2</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="9"/>
+        <v>0.12546847180044526</v>
+      </c>
+      <c r="V9" s="6">
+        <f t="shared" si="16"/>
+        <v>2.8540909090909081</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -1565,12 +3112,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E16932-AFD2-4F88-9876-424E09304D7D}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultColWidth="12.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" style="2" customWidth="1"/>
@@ -1578,45 +3125,45 @@
     <col min="8" max="9" width="9.54296875" style="2" customWidth="1"/>
     <col min="10" max="10" width="12" style="2" customWidth="1"/>
     <col min="11" max="11" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -1627,7 +3174,7 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>10.3116</v>
       </c>
       <c r="D2">
@@ -1659,7 +3206,7 @@
         <f>J2-C2</f>
         <v>0.90310000000000024</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="9">
         <f>(G2-K2)/G2</f>
         <v>8.0533496232945131E-2</v>
       </c>
@@ -1672,40 +3219,40 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>9.8409999999999993</v>
       </c>
       <c r="D3">
         <v>10.911199999999999</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E13" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E25" si="0">D3-C3</f>
         <v>1.0701999999999998</v>
       </c>
       <c r="F3" s="2">
         <v>10.889099999999999</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G13" si="1">F3-C3</f>
+        <f t="shared" ref="G3:G25" si="1">F3-C3</f>
         <v>1.0480999999999998</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H13" si="2">(E3-G3)/E3</f>
+        <f t="shared" ref="H3:H24" si="2">(E3-G3)/E3</f>
         <v>2.0650345729770148E-2</v>
       </c>
       <c r="I3" s="2">
-        <f t="shared" ref="I3:I13" si="3">(E3-G3)/G3</f>
+        <f t="shared" ref="I3:I24" si="3">(E3-G3)/G3</f>
         <v>2.1085774258181485E-2</v>
       </c>
       <c r="J3" s="2">
         <v>10.8</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3:K13" si="4">J3-C3</f>
+        <f t="shared" ref="K3:K25" si="4">J3-C3</f>
         <v>0.95900000000000141</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L13" si="5">(G3-K3)/G3</f>
+      <c r="L3" s="9">
+        <f t="shared" ref="L3:L25" si="5">(G3-K3)/G3</f>
         <v>8.5010972235472201E-2</v>
       </c>
     </row>
@@ -1717,7 +3264,7 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>10.1114</v>
       </c>
       <c r="D4">
@@ -1749,7 +3296,7 @@
         <f t="shared" si="4"/>
         <v>0.92689999999999984</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="9">
         <f t="shared" si="5"/>
         <v>8.3094272430507141E-2</v>
       </c>
@@ -1762,7 +3309,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>10.9634</v>
       </c>
       <c r="D5">
@@ -1794,7 +3341,7 @@
         <f t="shared" si="4"/>
         <v>0.91910000000000025</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="9">
         <f t="shared" si="5"/>
         <v>5.9744245524295601E-2</v>
       </c>
@@ -1807,7 +3354,7 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>10.7354</v>
       </c>
       <c r="D6">
@@ -1839,7 +3386,7 @@
         <f t="shared" si="4"/>
         <v>0.8990999999999989</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="9">
         <f t="shared" si="5"/>
         <v>5.9125156969444877E-2</v>
       </c>
@@ -1852,7 +3399,7 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>10.039199999999999</v>
       </c>
       <c r="D7">
@@ -1884,7 +3431,7 @@
         <f t="shared" si="4"/>
         <v>0.96380000000000088</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="9">
         <f t="shared" si="5"/>
         <v>5.796109862183587E-2</v>
       </c>
@@ -1892,12 +3439,12 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Characterization!A4</f>
-        <v>Rosemary</v>
+        <v>FGF Rosemary</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>10.7117</v>
       </c>
       <c r="D8">
@@ -1929,7 +3476,7 @@
         <f t="shared" si="4"/>
         <v>0.88999999999999879</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="9">
         <f t="shared" si="5"/>
         <v>7.8102340998550054E-2</v>
       </c>
@@ -1937,12 +3484,12 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Characterization!A4</f>
-        <v>Rosemary</v>
+        <v>FGF Rosemary</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>10.1225</v>
       </c>
       <c r="D9">
@@ -1974,7 +3521,7 @@
         <f t="shared" si="4"/>
         <v>0.89229999999999876</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="9">
         <f t="shared" si="5"/>
         <v>7.7153790464370986E-2</v>
       </c>
@@ -1982,12 +3529,12 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Characterization!A4</f>
-        <v>Rosemary</v>
+        <v>FGF Rosemary</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>9.7612000000000005</v>
       </c>
       <c r="D10">
@@ -2019,7 +3566,7 @@
         <f t="shared" si="4"/>
         <v>0.91629999999999967</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="9">
         <f t="shared" si="5"/>
         <v>7.5844679778114557E-2</v>
       </c>
@@ -2027,12 +3574,12 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Characterization!A5</f>
-        <v>Oregano</v>
+        <v>FGF Oregano</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>10.515499999999999</v>
       </c>
       <c r="D11">
@@ -2064,7 +3611,7 @@
         <f t="shared" si="4"/>
         <v>0.93580000000000041</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="9">
         <f t="shared" si="5"/>
         <v>6.8206711142089205E-2</v>
       </c>
@@ -2072,12 +3619,12 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Characterization!A5</f>
-        <v>Oregano</v>
+        <v>FGF Oregano</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>10.589</v>
       </c>
       <c r="D12">
@@ -2109,7 +3656,7 @@
         <f t="shared" si="4"/>
         <v>0.91479999999999961</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="9">
         <f t="shared" si="5"/>
         <v>7.0041679373792187E-2</v>
       </c>
@@ -2117,12 +3664,12 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Characterization!A5</f>
-        <v>Oregano</v>
+        <v>FGF Oregano</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>10.3164</v>
       </c>
       <c r="D13">
@@ -2154,9 +3701,549 @@
         <f t="shared" si="4"/>
         <v>0.90249999999999986</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="9">
         <f t="shared" si="5"/>
         <v>6.7857880603180834E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="str">
+        <f>Characterization!A6</f>
+        <v>FGF Buckwheat</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>9.8460000000000001</v>
+      </c>
+      <c r="D14">
+        <v>10.872</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1.0259999999999998</v>
+      </c>
+      <c r="F14">
+        <v>10.849</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0030000000000001</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="2"/>
+        <v>2.2417153996101065E-2</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2931206380857112E-2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>10.779400000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="4"/>
+        <v>0.93340000000000067</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" si="5"/>
+        <v>6.9391824526420176E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
+        <f>Characterization!A6</f>
+        <v>FGF Buckwheat</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10.2569</v>
+      </c>
+      <c r="D15">
+        <v>11.285500000000001</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>1.0286000000000008</v>
+      </c>
+      <c r="F15" s="2">
+        <v>11.260899999999999</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0039999999999996</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="2"/>
+        <v>2.3916002333269751E-2</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="3"/>
+        <v>2.4501992031873802E-2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>11.1943</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="4"/>
+        <v>0.93740000000000023</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" si="5"/>
+        <v>6.6334661354581034E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
+        <f>Characterization!A6</f>
+        <v>FGF Buckwheat</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10.313800000000001</v>
+      </c>
+      <c r="D16">
+        <v>11.3316</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>1.0177999999999994</v>
+      </c>
+      <c r="F16" s="2">
+        <v>11.309100000000001</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.9953000000000003</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="2"/>
+        <v>2.210650422479769E-2</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2606249372047693E-2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>11.2418</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="4"/>
+        <v>0.92799999999999905</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="5"/>
+        <v>6.7617803677284469E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
+        <f>Characterization!A7</f>
+        <v>FGF Sod</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>10.5273</v>
+      </c>
+      <c r="D17">
+        <v>11.450799999999999</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>0.92349999999999888</v>
+      </c>
+      <c r="F17" s="2">
+        <v>11.4245</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="1"/>
+        <v>0.89719999999999978</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="2"/>
+        <v>2.8478613968596789E-2</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="3"/>
+        <v>2.9313419527417641E-2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>11.3224</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="4"/>
+        <v>0.7950999999999997</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="5"/>
+        <v>0.11379848417298273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" t="str">
+        <f>Characterization!A7</f>
+        <v>FGF Sod</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>10.195499999999999</v>
+      </c>
+      <c r="D18">
+        <v>11.25</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>1.0545000000000009</v>
+      </c>
+      <c r="F18" s="2">
+        <v>11.221299999999999</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0258000000000003</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="2"/>
+        <v>2.721669037458567E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="3"/>
+        <v>2.7978163384675965E-2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>11.1023</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="4"/>
+        <v>0.90680000000000049</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="5"/>
+        <v>0.11600701891206838</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" t="str">
+        <f>Characterization!A7</f>
+        <v>FGF Sod</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>10.4476</v>
+      </c>
+      <c r="D19">
+        <v>11.540800000000001</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>1.0932000000000013</v>
+      </c>
+      <c r="F19" s="2">
+        <v>11.509399999999999</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0617999999999999</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="2"/>
+        <v>2.8723015001830762E-2</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="3"/>
+        <v>2.9572424185346988E-2</v>
+      </c>
+      <c r="J19" s="2">
+        <v>11.3871</v>
+      </c>
+      <c r="K19" s="2">
+        <f t="shared" si="4"/>
+        <v>0.93950000000000067</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="5"/>
+        <v>0.11518176681107478</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" t="str">
+        <f>Characterization!A8</f>
+        <v>FGF Sunflower</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>10.8154</v>
+      </c>
+      <c r="D20">
+        <v>11.8918</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>1.0763999999999996</v>
+      </c>
+      <c r="F20" s="2">
+        <v>11.868</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0526</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="2"/>
+        <v>2.2110739502043487E-2</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2610678320349232E-2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>11.7933</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="4"/>
+        <v>0.97789999999999999</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="5"/>
+        <v>7.0967129013870409E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" t="str">
+        <f>Characterization!A8</f>
+        <v>FGF Sunflower</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>10.759</v>
+      </c>
+      <c r="D21">
+        <v>11.8466</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>1.0876000000000001</v>
+      </c>
+      <c r="F21" s="2">
+        <v>11.8223</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0632999999999999</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="2"/>
+        <v>2.2342773078337815E-2</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2853380983730097E-2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>11.7485</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="4"/>
+        <v>0.9894999999999996</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="5"/>
+        <v>6.9406564469105911E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" t="str">
+        <f>Characterization!A8</f>
+        <v>FGF Sunflower</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>10.228899999999999</v>
+      </c>
+      <c r="D22">
+        <v>11.391299999999999</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>1.1623999999999999</v>
+      </c>
+      <c r="F22" s="2">
+        <v>11.3649</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="1"/>
+        <v>1.136000000000001</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="2"/>
+        <v>2.2711631108051335E-2</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="3"/>
+        <v>2.3239436619717294E-2</v>
+      </c>
+      <c r="J22" s="2">
+        <v>11.2849</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="4"/>
+        <v>1.0560000000000009</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="5"/>
+        <v>7.0422535211267609E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" t="str">
+        <f>Characterization!A9</f>
+        <v>FGF Corn</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>10.0923</v>
+      </c>
+      <c r="D23">
+        <v>11.2515</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>1.1592000000000002</v>
+      </c>
+      <c r="F23" s="2">
+        <v>11.226699999999999</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1343999999999994</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="2"/>
+        <v>2.1394064872326445E-2</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="3"/>
+        <v>2.186177715091752E-2</v>
+      </c>
+      <c r="J23" s="2">
+        <v>11.150700000000001</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="4"/>
+        <v>1.0584000000000007</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="5"/>
+        <v>6.6995768688292295E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" t="str">
+        <f>Characterization!A9</f>
+        <v>FGF Corn</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>10.1577</v>
+      </c>
+      <c r="D24">
+        <v>11.1866</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>1.0289000000000001</v>
+      </c>
+      <c r="F24" s="2">
+        <v>11.1624</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0046999999999997</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="2"/>
+        <v>2.3520264359996539E-2</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="3"/>
+        <v>2.4086792077237434E-2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>11.090299999999999</v>
+      </c>
+      <c r="K24" s="2">
+        <f t="shared" si="4"/>
+        <v>0.93259999999999899</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="5"/>
+        <v>7.1762715238380348E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" t="str">
+        <f>Characterization!A9</f>
+        <v>FGF Corn</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>10.3727</v>
+      </c>
+      <c r="D25">
+        <v>11.513999999999999</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>1.1412999999999993</v>
+      </c>
+      <c r="F25" s="2">
+        <v>11.487</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1143000000000001</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" ref="H25" si="6">(E25-G25)/E25</f>
+        <v>2.3657232979934516E-2</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" ref="I25" si="7">(E25-G25)/G25</f>
+        <v>2.4230458583863631E-2</v>
+      </c>
+      <c r="J25" s="2">
+        <v>11.4116</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" si="4"/>
+        <v>1.0388999999999999</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="5"/>
+        <v>6.7665799156421194E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2166,69 +4253,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1983686-5918-4241-A3F2-49C4CE6E45BD}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" customWidth="1"/>
-    <col min="6" max="7" width="6.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="7.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.36328125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.36328125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="3" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B2" t="str">
         <f>Characterization!$A$2</f>
@@ -2276,9 +4367,9 @@
         <v>9.6356628852166171E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B3" t="str">
         <f>Characterization!$A$2</f>
@@ -2327,9 +4418,9 @@
         <v>9.6289330632962869E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B4" t="str">
         <f>Characterization!$A$2</f>
@@ -2342,7 +4433,7 @@
         <v>46050</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E13" si="0">_xlfn.DAYS(D4,C4)</f>
+        <f t="shared" ref="E4:E43" si="0">_xlfn.DAYS(D4,C4)</f>
         <v>14</v>
       </c>
       <c r="F4" s="2">
@@ -2377,9 +4468,9 @@
         <v>9.629894466427763E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5" t="str">
         <f>Characterization!$A$2</f>
@@ -2427,9 +4518,9 @@
         <v>9.6149927178898878E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B6" t="str">
         <f>Characterization!$A$2</f>
@@ -2478,9 +4569,9 @@
         <v>9.6250874507703837E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B7" t="str">
         <f>Characterization!$A$2</f>
@@ -2528,9 +4619,9 @@
         <v>9.6260488539018599E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B8" t="str">
         <f>Characterization!$A$3</f>
@@ -2553,7 +4644,7 @@
       <c r="G8" s="2">
         <v>0.48680000000000001</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="10">
         <v>-122.78</v>
       </c>
       <c r="I8" s="2">
@@ -2577,10 +4668,13 @@
         <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B8, Characterization!A:A, 0))*F8</f>
         <v>6.8377879154377749E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B9" t="str">
         <f>Characterization!$A$3</f>
@@ -2603,7 +4697,7 @@
       <c r="G9" s="2">
         <v>0.50370000000000004</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="10">
         <v>-34.76</v>
       </c>
       <c r="I9" s="2">
@@ -2628,9 +4722,9 @@
         <v>6.8388135323442456E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10" t="str">
         <f>Characterization!$A$3</f>
@@ -2653,7 +4747,7 @@
       <c r="G10" s="2">
         <v>0.49830000000000002</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="10">
         <v>-59.35</v>
       </c>
       <c r="I10" s="2">
@@ -2677,10 +4771,13 @@
         <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B10, Characterization!A:A, 0))*F10</f>
         <v>6.8374460431356185E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B11" t="str">
         <f>Characterization!$A$3</f>
@@ -2703,7 +4800,7 @@
       <c r="G11" s="2">
         <v>0.50070000000000003</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="10">
         <v>-68.349999999999994</v>
       </c>
       <c r="I11" s="2">
@@ -2727,10 +4824,13 @@
         <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B11, Characterization!A:A, 0))*F11</f>
         <v>6.8432578722722834E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B12" t="str">
         <f>Characterization!$A$3</f>
@@ -2753,7 +4853,7 @@
       <c r="G12" s="2">
         <v>0.48420000000000002</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="10">
         <v>-47.12</v>
       </c>
       <c r="I12" s="2">
@@ -2778,9 +4878,9 @@
         <v>6.8579583812650266E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B13" t="str">
         <f>Characterization!$A$3</f>
@@ -2803,7 +4903,7 @@
       <c r="G13" s="2">
         <v>0.50729999999999997</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="10">
         <v>-114.39</v>
       </c>
       <c r="I13" s="2">
@@ -2828,100 +4928,2951 @@
         <v>6.8394972769485599E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="B14" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C14" s="4">
-        <v>46031</v>
+        <v>46086</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F14" s="2">
-        <f>2.0038-0.0083</f>
-        <v>1.9955000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+        <f>2.0065-0.0019</f>
+        <v>2.0045999999999999</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.49869999999999998</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-9.0299999999999994</v>
+      </c>
+      <c r="I14" s="2">
+        <v>10.1005</v>
+      </c>
+      <c r="J14" s="2">
+        <v>10.686400000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <v>10.661300000000001</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" ref="L14:L43" si="2">(J14-K14)/(K14-I14)</f>
+        <v>4.4757489300998758E-2</v>
+      </c>
+      <c r="M14" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B14, Characterization!A:A, 0))*L14/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B14, Characterization!A:A, 0))*0.01)</f>
+        <v>8.6554098540546853E-2</v>
+      </c>
+      <c r="N14" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B14, Characterization!A:A, 0))*F14</f>
+        <v>9.6361435867823558E-2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="B15" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C15" s="4">
-        <v>46031</v>
+        <v>46086</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F15" s="2">
-        <f>2.0063-0.0145</f>
-        <v>1.9918</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <f>2.0086-0.0016</f>
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.48170000000000002</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-5.18</v>
+      </c>
+      <c r="I15" s="2">
+        <v>10.0471</v>
+      </c>
+      <c r="J15" s="2">
+        <v>10.598800000000001</v>
+      </c>
+      <c r="K15" s="2">
+        <v>10.570499999999999</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="2"/>
+        <v>5.4069545280859027E-2</v>
+      </c>
+      <c r="M15" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B15, Characterization!A:A, 0))*L15/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B15, Characterization!A:A, 0))*0.01)</f>
+        <v>0.10456218218159971</v>
+      </c>
+      <c r="N15" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B15, Characterization!A:A, 0))*F15</f>
+        <v>9.6476804243600667E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="B16" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C16" s="4">
-        <v>46031</v>
+        <v>46086</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
-        <f>2.0138-0.0145</f>
-        <v>1.9992999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <f>2.0077-0.0016</f>
+        <v>2.0061</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.4708</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-5.78</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10.278499999999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>10.823700000000001</v>
+      </c>
+      <c r="K16" s="2">
+        <v>10.7981</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="2"/>
+        <v>4.9268668206313912E-2</v>
+      </c>
+      <c r="M16" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B16, Characterization!A:A, 0))*L16/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B16, Characterization!A:A, 0))*0.01)</f>
+        <v>9.5278024515902462E-2</v>
+      </c>
+      <c r="N16" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B16, Characterization!A:A, 0))*F16</f>
+        <v>9.6433541102684248E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="B17" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C17" s="4">
-        <v>46031</v>
+        <v>46086</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F17" s="2">
-        <f>2.0277-0.0147</f>
-        <v>2.0129999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <f>2.003-0.0015</f>
+        <v>2.0015000000000001</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.50519999999999998</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10.3347</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10.928100000000001</v>
+      </c>
+      <c r="K17" s="2">
+        <v>10.8734</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.10154074624095114</v>
+      </c>
+      <c r="M17" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B17, Characterization!A:A, 0))*L17/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B17, Characterization!A:A, 0))*0.01)</f>
+        <v>0.19636418157673172</v>
+      </c>
+      <c r="N17" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B17, Characterization!A:A, 0))*F17</f>
+        <v>9.6212418382444806E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="B18" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C18" s="4">
-        <v>46031</v>
+        <v>46086</v>
+      </c>
+      <c r="D18" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="F18" s="2">
-        <f>2.0169-0.0108</f>
-        <v>2.0061</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <f>2.0087-0.0028</f>
+        <v>2.0059</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.50270000000000004</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1.48</v>
+      </c>
+      <c r="I18" s="2">
+        <v>10.822699999999999</v>
+      </c>
+      <c r="J18" s="2">
+        <v>11.4642</v>
+      </c>
+      <c r="K18" s="2">
+        <v>11.4079</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="2"/>
+        <v>9.620642515379392E-2</v>
+      </c>
+      <c r="M18" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B18, Characterization!A:A, 0))*L18/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B18, Characterization!A:A, 0))*0.01)</f>
+        <v>0.18604842525895229</v>
+      </c>
+      <c r="N18" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B18, Characterization!A:A, 0))*F18</f>
+        <v>9.6423927071369486E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B19" t="str">
         <f>Characterization!$A$2</f>
         <v>Soybean Undisturbed</v>
       </c>
       <c r="C19" s="4">
+        <v>46086</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F19" s="2">
+        <f>2.0026-0.001</f>
+        <v>2.0016000000000003</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.50929999999999997</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-1.66</v>
+      </c>
+      <c r="I19" s="2">
+        <v>10.010999999999999</v>
+      </c>
+      <c r="J19" s="2">
+        <v>10.5215</v>
+      </c>
+      <c r="K19" s="2">
+        <v>10.485799999999999</v>
+      </c>
+      <c r="L19" s="2">
+        <f t="shared" si="2"/>
+        <v>7.518955349620951E-2</v>
+      </c>
+      <c r="M19" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B19, Characterization!A:A, 0))*L19/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B19, Characterization!A:A, 0))*0.01)</f>
+        <v>0.14540502883805442</v>
+      </c>
+      <c r="N19" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B19, Characterization!A:A, 0))*F19</f>
+        <v>9.6217225398102194E-2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C20" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F20" s="2">
+        <f>2.0038-0.0014</f>
+        <v>2.0024000000000002</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.496</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-5.72</v>
+      </c>
+      <c r="I20" s="2">
+        <v>10.6744</v>
+      </c>
+      <c r="J20" s="2">
+        <v>11.2348</v>
+      </c>
+      <c r="K20" s="2">
+        <v>11.2096</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="2"/>
+        <v>4.7085201793721797E-2</v>
+      </c>
+      <c r="M20" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B20, Characterization!A:A, 0))*L20/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B20, Characterization!A:A, 0))*0.01)</f>
+        <v>0.11055213004484259</v>
+      </c>
+      <c r="N20" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B20, Characterization!A:A, 0))*F20</f>
+        <v>6.8456509783873812E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C21" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F21" s="2">
+        <f>2.0057-0.0015</f>
+        <v>2.0042</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.49769999999999998</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-6.49</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10.7262</v>
+      </c>
+      <c r="J21" s="2">
+        <v>11.282</v>
+      </c>
+      <c r="K21" s="2">
+        <v>11.259399999999999</v>
+      </c>
+      <c r="L21" s="2">
+        <f t="shared" si="2"/>
+        <v>4.2385596399101014E-2</v>
+      </c>
+      <c r="M21" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B21, Characterization!A:A, 0))*L21/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B21, Characterization!A:A, 0))*0.01)</f>
+        <v>9.9517848212055879E-2</v>
+      </c>
+      <c r="N21" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B21, Characterization!A:A, 0))*F21</f>
+        <v>6.8518046798262039E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C22" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D22" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F22" s="2">
+        <f>2.0055-0.0019</f>
+        <v>2.0036</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.48559999999999998</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-11.78</v>
+      </c>
+      <c r="I22" s="2">
+        <v>10.357699999999999</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10.9011</v>
+      </c>
+      <c r="K22" s="2">
+        <v>10.8789</v>
+      </c>
+      <c r="L22" s="2">
+        <f t="shared" si="2"/>
+        <v>4.2594013814274294E-2</v>
+      </c>
+      <c r="M22" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B22, Characterization!A:A, 0))*L22/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B22, Characterization!A:A, 0))*0.01)</f>
+        <v>0.10000719493476481</v>
+      </c>
+      <c r="N22" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B22, Characterization!A:A, 0))*F22</f>
+        <v>6.8497534460132625E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C23" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D23" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F23" s="2">
+        <f>2.008-0.0022</f>
+        <v>2.0057999999999998</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.49070000000000003</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-0.83</v>
+      </c>
+      <c r="I23" s="2">
+        <v>10.2479</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10.811500000000001</v>
+      </c>
+      <c r="K23" s="2">
+        <v>10.750999999999999</v>
+      </c>
+      <c r="L23" s="2">
+        <f t="shared" si="2"/>
+        <v>0.12025442258000621</v>
+      </c>
+      <c r="M23" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B23, Characterization!A:A, 0))*L23/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B23, Characterization!A:A, 0))*0.01)</f>
+        <v>0.28234736301597274</v>
+      </c>
+      <c r="N23" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B23, Characterization!A:A, 0))*F23</f>
+        <v>6.857274636660711E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C24" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <f>2.0092-0.0022</f>
+        <v>2.0069999999999997</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.50360000000000005</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-1.36</v>
+      </c>
+      <c r="I24" s="2">
+        <v>10.2066</v>
+      </c>
+      <c r="J24" s="2">
+        <v>10.7446</v>
+      </c>
+      <c r="K24" s="2">
+        <v>10.701599999999999</v>
+      </c>
+      <c r="L24" s="2">
+        <f t="shared" si="2"/>
+        <v>8.6868686868689107E-2</v>
+      </c>
+      <c r="M24" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B24, Characterization!A:A, 0))*L24/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B24, Characterization!A:A, 0))*0.01)</f>
+        <v>0.20396043771044287</v>
+      </c>
+      <c r="N24" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B24, Characterization!A:A, 0))*F24</f>
+        <v>6.8613771042865923E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="str">
+        <f>Characterization!$A$3</f>
+        <v>Soybean Center</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46087</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46091</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2.0055000000000001</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.49209999999999998</v>
+      </c>
+      <c r="H25" s="3">
+        <v>-3.92</v>
+      </c>
+      <c r="I25" s="2">
+        <v>10.196</v>
+      </c>
+      <c r="J25" s="2">
+        <v>10.733499999999999</v>
+      </c>
+      <c r="K25" s="2">
+        <v>10.703099999999999</v>
+      </c>
+      <c r="L25" s="2">
+        <f t="shared" si="2"/>
+        <v>5.9948728061526797E-2</v>
+      </c>
+      <c r="M25" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B25, Characterization!A:A, 0))*L25/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B25, Characterization!A:A, 0))*0.01)</f>
+        <v>0.14075461776112638</v>
+      </c>
+      <c r="N25" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B25, Characterization!A:A, 0))*F25</f>
+        <v>6.8562490197542417E-2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D26" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F26" s="2">
+        <f>2.0076-0.0031</f>
+        <v>2.0045000000000002</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.49919999999999998</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-29.15</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9.9129000000000005</v>
+      </c>
+      <c r="J26" s="2">
+        <v>10.434900000000001</v>
+      </c>
+      <c r="K26" s="2">
+        <v>10.418799999999999</v>
+      </c>
+      <c r="L26" s="2">
+        <f t="shared" si="2"/>
+        <v>3.1824471239378531E-2</v>
+      </c>
+      <c r="M26" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B26, Characterization!A:A, 0))*L26/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B26, Characterization!A:A, 0))*0.01)</f>
+        <v>9.5443104697907594E-2</v>
+      </c>
+      <c r="N26" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B26, Characterization!A:A, 0))*F26</f>
+        <v>7.9873737288577634E-2</v>
+      </c>
+      <c r="O26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <f>2.0015-0.0026</f>
+        <v>1.9989000000000001</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.49780000000000002</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-42.2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>10.446300000000001</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10.9688</v>
+      </c>
+      <c r="K27" s="2">
+        <v>10.953799999999999</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="2"/>
+        <v>2.9556650246306625E-2</v>
+      </c>
+      <c r="M27" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B27, Characterization!A:A, 0))*L27/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B27, Characterization!A:A, 0))*0.01)</f>
+        <v>8.8641801548209082E-2</v>
+      </c>
+      <c r="N27" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B27, Characterization!A:A, 0))*F27</f>
+        <v>7.9650592899046066E-2</v>
+      </c>
+      <c r="O27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D28" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <f>2.0057-0.0022</f>
+        <v>2.0034999999999998</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.5091</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-22.68</v>
+      </c>
+      <c r="I28" s="2">
+        <v>10.026</v>
+      </c>
+      <c r="J28" s="2">
+        <v>10.5181</v>
+      </c>
+      <c r="K28" s="2">
+        <v>10.5007</v>
+      </c>
+      <c r="L28" s="2">
+        <f t="shared" si="2"/>
+        <v>3.6654729302718118E-2</v>
+      </c>
+      <c r="M28" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B28, Characterization!A:A, 0))*L28/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B28, Characterization!A:A, 0))*0.01)</f>
+        <v>0.10992927864215174</v>
+      </c>
+      <c r="N28" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B28, Characterization!A:A, 0))*F28</f>
+        <v>7.9833890076161276E-2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F29" s="2">
+        <f>2.0084-0.0031</f>
+        <v>2.0053000000000001</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.50819999999999999</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-8</v>
+      </c>
+      <c r="I29" s="2">
+        <v>11.690099999999999</v>
+      </c>
+      <c r="J29" s="2">
+        <v>12.209199999999999</v>
+      </c>
+      <c r="K29" s="2">
+        <v>12.180899999999999</v>
+      </c>
+      <c r="L29" s="2">
+        <f t="shared" si="2"/>
+        <v>5.766096169519104E-2</v>
+      </c>
+      <c r="M29" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B29, Characterization!A:A, 0))*L29/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B29, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17292796988395862</v>
+      </c>
+      <c r="N29" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B29, Characterization!A:A, 0))*F29</f>
+        <v>7.9905615058510709E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D30" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F30" s="2">
+        <f>2.005-0.0032</f>
+        <v>2.0017999999999998</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.49930000000000002</v>
+      </c>
+      <c r="H30" s="3">
+        <v>-8.5399999999999991</v>
+      </c>
+      <c r="I30" s="2">
+        <v>11.7432</v>
+      </c>
+      <c r="J30" s="2">
+        <v>12.2882</v>
+      </c>
+      <c r="K30" s="2">
+        <v>12.262600000000001</v>
+      </c>
+      <c r="L30" s="2">
+        <f t="shared" si="2"/>
+        <v>4.9287639584133437E-2</v>
+      </c>
+      <c r="M30" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B30, Characterization!A:A, 0))*L30/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B30, Characterization!A:A, 0))*0.01)</f>
+        <v>0.14781597814327252</v>
+      </c>
+      <c r="N30" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B30, Characterization!A:A, 0))*F30</f>
+        <v>7.9766149815053464E-2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="4">
+        <v>46091</v>
+      </c>
+      <c r="D31" s="4">
+        <v>46095</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F31" s="2">
+        <f>2.0053-0.0036</f>
+        <v>2.0017</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.49780000000000002</v>
+      </c>
+      <c r="H31" s="3">
+        <v>-3.74</v>
+      </c>
+      <c r="I31" s="2">
+        <v>11.7173</v>
+      </c>
+      <c r="J31" s="2">
+        <v>12.233700000000001</v>
+      </c>
+      <c r="K31" s="2">
+        <v>12.2058</v>
+      </c>
+      <c r="L31" s="2">
+        <f t="shared" si="2"/>
+        <v>5.711361310133202E-2</v>
+      </c>
+      <c r="M31" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B31, Characterization!A:A, 0))*L31/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B31, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17128644538675664</v>
+      </c>
+      <c r="N31" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B31, Characterization!A:A, 0))*F31</f>
+        <v>7.9762165093811843E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F32" s="2">
+        <f>2.0056-0.0022</f>
+        <v>2.0033999999999996</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.50819999999999999</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-26.42</v>
+      </c>
+      <c r="I32" s="2">
+        <v>10.7102</v>
+      </c>
+      <c r="J32" s="2">
+        <v>11.2226</v>
+      </c>
+      <c r="K32" s="2">
+        <v>11.2075</v>
+      </c>
+      <c r="L32" s="2">
+        <f t="shared" si="2"/>
+        <v>3.0363965413232174E-2</v>
+      </c>
+      <c r="M32" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B32, Characterization!A:A, 0))*L32/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B32, Characterization!A:A, 0))*0.01)</f>
+        <v>8.7144580735976349E-2</v>
+      </c>
+      <c r="N32" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B32, Characterization!A:A, 0))*F32</f>
+        <v>8.951089061312284E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D33" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F33" s="2">
+        <f>2.0052-0.0037</f>
+        <v>2.0015000000000001</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.49490000000000001</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-22.36</v>
+      </c>
+      <c r="I33" s="2">
+        <v>10.151999999999999</v>
+      </c>
+      <c r="J33" s="2">
+        <v>10.6524</v>
+      </c>
+      <c r="K33" s="2">
+        <v>10.636699999999999</v>
+      </c>
+      <c r="L33" s="2">
+        <f t="shared" si="2"/>
+        <v>3.2391169795751414E-2</v>
+      </c>
+      <c r="M33" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B33, Characterization!A:A, 0))*L33/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B33, Characterization!A:A, 0))*0.01)</f>
+        <v>9.2962657313806568E-2</v>
+      </c>
+      <c r="N33" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B33, Characterization!A:A, 0))*F33</f>
+        <v>8.9425999581793647E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D34" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F34" s="2">
+        <f>2.0048-0.0038</f>
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.50880000000000003</v>
+      </c>
+      <c r="H34" s="3">
+        <v>-19.760000000000002</v>
+      </c>
+      <c r="I34" s="2">
+        <v>9.8386999999999993</v>
+      </c>
+      <c r="J34" s="2">
+        <v>10.3431</v>
+      </c>
+      <c r="K34" s="2">
+        <v>10.325200000000001</v>
+      </c>
+      <c r="L34" s="2">
+        <f t="shared" si="2"/>
+        <v>3.6793422404931331E-2</v>
+      </c>
+      <c r="M34" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B34, Characterization!A:A, 0))*L34/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B34, Characterization!A:A, 0))*0.01)</f>
+        <v>0.10559712230215294</v>
+      </c>
+      <c r="N34" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B34, Characterization!A:A, 0))*F34</f>
+        <v>8.940365983670702E-2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D35" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <f>2.0058-0.0051</f>
+        <v>2.0006999999999997</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.49220000000000003</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-5.71</v>
+      </c>
+      <c r="I35" s="2">
+        <v>10.2281</v>
+      </c>
+      <c r="J35" s="2">
+        <v>10.800800000000001</v>
+      </c>
+      <c r="K35" s="2">
+        <v>10.7689</v>
+      </c>
+      <c r="L35" s="2">
+        <f t="shared" si="2"/>
+        <v>5.8986686390532936E-2</v>
+      </c>
+      <c r="M35" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B35, Characterization!A:A, 0))*L35/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B35, Characterization!A:A, 0))*0.01)</f>
+        <v>0.16929178994082958</v>
+      </c>
+      <c r="N35" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B35, Characterization!A:A, 0))*F35</f>
+        <v>8.9390255989655026E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D36" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F36" s="2">
+        <f>2.0044-0.0053</f>
+        <v>1.9990999999999999</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.501</v>
+      </c>
+      <c r="H36" s="3">
+        <v>-6.5</v>
+      </c>
+      <c r="I36" s="2">
+        <v>10.6739</v>
+      </c>
+      <c r="J36" s="2">
+        <v>11.2195</v>
+      </c>
+      <c r="K36" s="2">
+        <v>11.187799999999999</v>
+      </c>
+      <c r="L36" s="2">
+        <f t="shared" si="2"/>
+        <v>6.1685152753455444E-2</v>
+      </c>
+      <c r="M36" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B36, Characterization!A:A, 0))*L36/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B36, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17703638840241714</v>
+      </c>
+      <c r="N36" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B36, Characterization!A:A, 0))*F36</f>
+        <v>8.9318768805377799E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="4">
+        <v>46092</v>
+      </c>
+      <c r="D37" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F37" s="2">
+        <f>2.0036-0.0056</f>
+        <v>1.998</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.503</v>
+      </c>
+      <c r="H37" s="3">
+        <v>-4.87</v>
+      </c>
+      <c r="I37" s="2">
+        <v>10.534800000000001</v>
+      </c>
+      <c r="J37" s="2">
+        <v>11.0832</v>
+      </c>
+      <c r="K37" s="2">
+        <v>11.0505</v>
+      </c>
+      <c r="L37" s="2">
+        <f t="shared" si="2"/>
+        <v>6.3408958696917275E-2</v>
+      </c>
+      <c r="M37" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B37, Characterization!A:A, 0))*L37/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B37, Characterization!A:A, 0))*0.01)</f>
+        <v>0.1819837114601526</v>
+      </c>
+      <c r="N37" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B37, Characterization!A:A, 0))*F37</f>
+        <v>8.9269621366187213E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D38" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F38" s="2">
+        <f>2.0078-0.004</f>
+        <v>2.0038</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0.49380000000000002</v>
+      </c>
+      <c r="H38" s="3">
+        <v>-29.42</v>
+      </c>
+      <c r="I38" s="2">
+        <v>10.369400000000001</v>
+      </c>
+      <c r="J38" s="2">
+        <v>10.8992</v>
+      </c>
+      <c r="K38" s="2">
+        <v>10.870699999999999</v>
+      </c>
+      <c r="L38" s="2">
+        <f t="shared" si="2"/>
+        <v>5.6852184320768308E-2</v>
+      </c>
+      <c r="M38" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B38, Characterization!A:A, 0))*L38/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B38, Characterization!A:A, 0))*0.01)</f>
+        <v>0.12152154398564229</v>
+      </c>
+      <c r="N38" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B38, Characterization!A:A, 0))*F38</f>
+        <v>0.13364852834078569</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" t="s">
+        <v>161</v>
+      </c>
+      <c r="C39" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D39" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <f>2.0046-0.0031</f>
+        <v>2.0015000000000001</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0.50290000000000001</v>
+      </c>
+      <c r="H39" s="3">
+        <v>-25.4</v>
+      </c>
+      <c r="I39" s="2">
+        <v>10.393800000000001</v>
+      </c>
+      <c r="J39" s="2">
+        <v>10.902799999999999</v>
+      </c>
+      <c r="K39" s="2">
+        <v>10.8775</v>
+      </c>
+      <c r="L39" s="2">
+        <f t="shared" si="2"/>
+        <v>5.230514781889542E-2</v>
+      </c>
+      <c r="M39" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B39, Characterization!A:A, 0))*L39/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B39, Characterization!A:A, 0))*0.01)</f>
+        <v>0.11180225346288898</v>
+      </c>
+      <c r="N39" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B39, Characterization!A:A, 0))*F39</f>
+        <v>0.13349512400143854</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D40" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <f>2.0049-0.0023</f>
+        <v>2.0026000000000002</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.50290000000000001</v>
+      </c>
+      <c r="H40" s="3">
+        <v>-18.5</v>
+      </c>
+      <c r="I40" s="2">
+        <v>10.099</v>
+      </c>
+      <c r="J40" s="2">
+        <v>10.6288</v>
+      </c>
+      <c r="K40" s="2">
+        <v>10.601100000000001</v>
+      </c>
+      <c r="L40" s="2">
+        <f t="shared" si="2"/>
+        <v>5.5168293168690236E-2</v>
+      </c>
+      <c r="M40" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B40, Characterization!A:A, 0))*L40/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B40, Characterization!A:A, 0))*0.01)</f>
+        <v>0.11792222664807539</v>
+      </c>
+      <c r="N40" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B40, Characterization!A:A, 0))*F40</f>
+        <v>0.13356849129416978</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D41" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <f>2.0045-0.0024</f>
+        <v>2.0021</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.50619999999999998</v>
+      </c>
+      <c r="H41" s="3">
+        <v>-4.4400000000000004</v>
+      </c>
+      <c r="I41" s="2">
+        <v>10.409800000000001</v>
+      </c>
+      <c r="J41" s="2">
+        <v>10.9655</v>
+      </c>
+      <c r="K41" s="2">
+        <v>10.9185</v>
+      </c>
+      <c r="L41" s="2">
+        <f t="shared" si="2"/>
+        <v>9.2392372714764429E-2</v>
+      </c>
+      <c r="M41" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B41, Characterization!A:A, 0))*L41/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B41, Characterization!A:A, 0))*0.01)</f>
+        <v>0.19748869667780899</v>
+      </c>
+      <c r="N41" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B41, Characterization!A:A, 0))*F41</f>
+        <v>0.13353514252474649</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D42" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <f>2.0045-0.0024</f>
+        <v>2.0021</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.48930000000000001</v>
+      </c>
+      <c r="H42" s="3">
+        <v>-4.37</v>
+      </c>
+      <c r="I42" s="2">
+        <v>10.1736</v>
+      </c>
+      <c r="J42" s="2">
+        <v>10.7921</v>
+      </c>
+      <c r="K42" s="2">
+        <v>10.739000000000001</v>
+      </c>
+      <c r="L42" s="2">
+        <f t="shared" si="2"/>
+        <v>9.3915811814642342E-2</v>
+      </c>
+      <c r="M42" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B42, Characterization!A:A, 0))*L42/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B42, Characterization!A:A, 0))*0.01)</f>
+        <v>0.20074504775379801</v>
+      </c>
+      <c r="N42" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B42, Characterization!A:A, 0))*F42</f>
+        <v>0.13353514252474649</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="4">
+        <v>46096</v>
+      </c>
+      <c r="D43" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F43" s="2">
+        <f>2.0037-0.0035</f>
+        <v>2.0002</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.49780000000000002</v>
+      </c>
+      <c r="H43" s="3">
+        <v>-3.97</v>
+      </c>
+      <c r="I43" s="2">
+        <v>10.8683</v>
+      </c>
+      <c r="J43" s="2">
+        <v>11.4085</v>
+      </c>
+      <c r="K43" s="2">
+        <v>11.362399999999999</v>
+      </c>
+      <c r="L43" s="2">
+        <f t="shared" si="2"/>
+        <v>9.3300951224450437E-2</v>
+      </c>
+      <c r="M43" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B43, Characterization!A:A, 0))*L43/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B43, Characterization!A:A, 0))*0.01)</f>
+        <v>0.19943078324226282</v>
+      </c>
+      <c r="N43" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B43, Characterization!A:A, 0))*F43</f>
+        <v>0.13340841720093799</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="F44" s="2">
+        <f>2.0083-0.002</f>
+        <v>2.0063000000000004</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="M44" s="9"/>
+      <c r="N44" s="8"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="F45" s="2">
+        <f>2.0048-0.0029</f>
+        <v>2.0019</v>
+      </c>
+      <c r="M45" s="9"/>
+      <c r="N45" s="8"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="F46" s="2">
+        <f>2.0052-0.0021</f>
+        <v>2.0030999999999999</v>
+      </c>
+      <c r="M46" s="9"/>
+      <c r="N46" s="8"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="F47" s="2">
+        <f>2.0041-0.0034</f>
+        <v>2.0007000000000001</v>
+      </c>
+      <c r="M47" s="9"/>
+      <c r="N47" s="8"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="F48" s="2">
+        <f>2.0013-0.0017</f>
+        <v>1.9996</v>
+      </c>
+      <c r="M48" s="9"/>
+      <c r="N48" s="8"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46098</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="F49" s="2">
+        <f>2.0024-0.0027</f>
+        <v>1.9997000000000003</v>
+      </c>
+      <c r="M49" s="9"/>
+      <c r="N49" s="8"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="F50" s="2">
+        <f>2.002-0.0013</f>
+        <v>2.0006999999999997</v>
+      </c>
+      <c r="M50" s="9"/>
+      <c r="N50" s="8"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="F51" s="2">
+        <f>2.0021-0.0009</f>
+        <v>2.0011999999999999</v>
+      </c>
+      <c r="M51" s="9"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="F52" s="2">
+        <f>2.0036-0.0017</f>
+        <v>2.0019</v>
+      </c>
+      <c r="M52" s="9"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="F53" s="2">
+        <f>2.0085-0.0019</f>
+        <v>2.0066000000000002</v>
+      </c>
+      <c r="M53" s="9"/>
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="F54" s="2">
+        <f>2.0032-0.0025</f>
+        <v>2.0007000000000001</v>
+      </c>
+      <c r="M54" s="9"/>
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="4">
+        <v>46100</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="F55" s="2">
+        <f>2.0021-0.0037</f>
+        <v>1.9984</v>
+      </c>
+      <c r="M55" s="9"/>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="8"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="8"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="8"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="8"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>200</v>
+      </c>
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="8"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="8"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C62" s="4">
         <v>46031</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F62" s="2">
+        <f>2.0038-0.0083</f>
+        <v>1.9955000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46031</v>
+      </c>
+      <c r="F63" s="2">
+        <f>2.0063-0.0145</f>
+        <v>1.9918</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C64" s="4">
+        <v>46031</v>
+      </c>
+      <c r="F64" s="2">
+        <f>2.0138-0.0145</f>
+        <v>1.9992999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46031</v>
+      </c>
+      <c r="F65" s="2">
+        <f>2.0277-0.0147</f>
+        <v>2.0129999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C66" s="4">
+        <v>46031</v>
+      </c>
+      <c r="F66" s="2">
+        <f>2.0169-0.0108</f>
+        <v>2.0061</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="str">
+        <f>Characterization!$A$2</f>
+        <v>Soybean Undisturbed</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46031</v>
+      </c>
+      <c r="F67" s="2">
         <f>2.0203-0.0114</f>
         <v>2.0089000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCD1671-150A-431B-9802-17D2A2E7407A}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.90625" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="4">
+        <v>45831</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="4">
+        <v>45857</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="4">
+        <v>45857</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="4">
+        <v>45954</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="4">
+        <v>45947</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F465DB-3416-4852-B573-96C6ABA2B1A8}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="4">
+        <v>45831</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="4">
+        <v>45857</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="4">
+        <v>45857</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="4">
+        <v>45954</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45947</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF4ED8B-9D6A-4DCD-8C9F-6E04025006A7}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B2">
+        <v>657692</v>
+      </c>
+      <c r="C2">
+        <v>132652</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B3">
+        <v>648202</v>
+      </c>
+      <c r="C3">
+        <v>110470</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B4">
+        <v>665511</v>
+      </c>
+      <c r="C4">
+        <v>111721</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B5">
+        <v>658318</v>
+      </c>
+      <c r="C5">
+        <v>118142</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B6">
+        <v>652051</v>
+      </c>
+      <c r="C6">
+        <v>113691</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46035</v>
+      </c>
+      <c r="E6">
+        <f>AVERAGE(B2:B6)</f>
+        <v>656354.80000000005</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.STDEV.S(B2:B6)</f>
+        <v>6604.337567084227</v>
+      </c>
+      <c r="G6">
+        <f>MAX(B2:B6)-MIN(B2:B6)</f>
+        <v>17309</v>
+      </c>
+      <c r="H6">
+        <f>AVERAGE(C2:C6)</f>
+        <v>117335.2</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.STDEV.S(C2:C6)</f>
+        <v>9044.1375321254382</v>
+      </c>
+      <c r="J6">
+        <f>E6/A6</f>
+        <v>593449.18625678122</v>
+      </c>
+      <c r="K6">
+        <f>G6/J6</f>
+        <v>2.9166776871289733E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>538634</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>528844</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>543785</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>522798</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46056</v>
+      </c>
+      <c r="E10">
+        <f>AVERAGE(B7:B10)</f>
+        <v>533515.25</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.STDEV.S(B7:B10)</f>
+        <v>9457.7902766273401</v>
+      </c>
+      <c r="G10">
+        <f>MAX(B7:B10)-MIN(B7:B10)</f>
+        <v>20987</v>
+      </c>
+      <c r="J10">
+        <f>E10/A10</f>
+        <v>533515.25</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ref="K10:K15" si="0">G10/J10</f>
+        <v>3.9337207324439183E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B11">
+        <v>714044</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B12">
+        <v>704231</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B13">
+        <v>709233</v>
+      </c>
+      <c r="D13" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B14">
+        <v>697764</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="B15">
+        <v>683599</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46056</v>
+      </c>
+      <c r="E15">
+        <f>AVERAGE(B11:B15)</f>
+        <v>701774.2</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.STDEV.S(B11:B15)</f>
+        <v>11817.753115546118</v>
+      </c>
+      <c r="G15">
+        <f>MAX(B11:B15)-MIN(B11:B15)</f>
+        <v>30445</v>
+      </c>
+      <c r="J15">
+        <f>E15/A15</f>
+        <v>634515.55153707042</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>4.7981487492700654E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2930,340 +7881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F465DB-3416-4852-B573-96C6ABA2B1A8}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="4">
-        <v>45831</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="4">
-        <v>45857</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="4">
-        <v>45857</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="4">
-        <v>45954</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="4">
-        <v>45947</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD63824-F95F-4A24-9AAE-5CBB9DC71786}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3274,27 +7892,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>42</v>
-      </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4">
         <v>46050</v>
@@ -3305,7 +7923,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4">
         <v>46050</v>
@@ -3319,7 +7937,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4">
         <v>46050</v>
@@ -3330,7 +7948,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4">
         <v>46050</v>
@@ -3341,7 +7959,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4">
         <v>46050</v>
@@ -3355,7 +7973,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4">
         <v>46050</v>
@@ -3372,7 +7990,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4">
         <v>46050</v>
@@ -3389,7 +8007,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4">
         <v>46050</v>
@@ -3406,7 +8024,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4">
         <v>46050</v>
@@ -3423,7 +8041,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4">
         <v>46050</v>
@@ -3440,7 +8058,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B12" s="4">
         <v>46050</v>
@@ -3457,7 +8075,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B13" s="4">
         <v>46050</v>
@@ -3474,7 +8092,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4">
         <v>46050</v>
@@ -3491,7 +8109,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B15" s="4">
         <v>46050</v>
@@ -3508,7 +8126,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4">
         <v>46050</v>
@@ -3525,7 +8143,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4">
         <v>46050</v>
@@ -3536,7 +8154,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B18" s="4">
         <v>46050</v>
@@ -3547,7 +8165,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" s="4">
         <v>46050</v>
@@ -3558,7 +8176,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B20" s="4">
         <v>46050</v>
@@ -3569,7 +8187,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B21" s="4">
         <v>46050</v>
@@ -3631,238 +8249,6 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" s="4">
         <v>46050</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF4ED8B-9D6A-4DCD-8C9F-6E04025006A7}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B2">
-        <v>657692</v>
-      </c>
-      <c r="C2">
-        <v>132652</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B3">
-        <v>648202</v>
-      </c>
-      <c r="C3">
-        <v>110470</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B4">
-        <v>665511</v>
-      </c>
-      <c r="C4">
-        <v>111721</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B5">
-        <v>658318</v>
-      </c>
-      <c r="C5">
-        <v>118142</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B6">
-        <v>652051</v>
-      </c>
-      <c r="C6">
-        <v>113691</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46035</v>
-      </c>
-      <c r="E6">
-        <f>AVERAGE(B2:B6)</f>
-        <v>656354.80000000005</v>
-      </c>
-      <c r="F6">
-        <f>_xlfn.STDEV.S(B2:B6)</f>
-        <v>6604.337567084227</v>
-      </c>
-      <c r="G6">
-        <f>AVERAGE(C2:C6)</f>
-        <v>117335.2</v>
-      </c>
-      <c r="H6">
-        <f>_xlfn.STDEV.S(C2:C6)</f>
-        <v>9044.1375321254382</v>
-      </c>
-      <c r="I6">
-        <f>E6/A6</f>
-        <v>593449.18625678122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>538634</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>528844</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>543785</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>522798</v>
-      </c>
-      <c r="E10">
-        <f>AVERAGE(B7:B10)</f>
-        <v>533515.25</v>
-      </c>
-      <c r="F10">
-        <f>_xlfn.STDEV.S(B7:B10)</f>
-        <v>9457.7902766273401</v>
-      </c>
-      <c r="I10">
-        <f>E10/A10</f>
-        <v>533515.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B11">
-        <v>714044</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B12">
-        <v>704231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B13">
-        <v>709233</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B14">
-        <v>697764</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="B15">
-        <v>683599</v>
-      </c>
-      <c r="E15">
-        <f>AVERAGE(B11:B15)</f>
-        <v>701774.2</v>
-      </c>
-      <c r="F15">
-        <f>_xlfn.STDEV.S(B11:B15)</f>
-        <v>11817.753115546118</v>
-      </c>
-      <c r="I15">
-        <f>E15/A15</f>
-        <v>634515.55153707042</v>
       </c>
     </row>
   </sheetData>

--- a/Farm Soils Data.xlsx
+++ b/Farm Soils Data.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://princetonu-my.sharepoint.com/personal/cg3403_princeton_edu/Documents/Undergraduate Research/Thesis Files/Thesis Rmd Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1835" documentId="11_F25DC773A252ABDACC1048EB41DB448A5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D002BF18-488B-4409-8D9A-9FE48655C303}"/>
+  <xr:revisionPtr revIDLastSave="2361" documentId="11_F25DC773A252ABDACC1048EB41DB448A5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78957F7A-7803-43E8-8B02-49C4480BC9AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="884" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="8100" windowWidth="19420" windowHeight="10300" tabRatio="884" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="1" r:id="rId1"/>
     <sheet name="Oven Drying &amp; Combustion" sheetId="2" r:id="rId2"/>
     <sheet name="Trial Metadata" sheetId="7" r:id="rId3"/>
-    <sheet name="Soil Samples for Rutgers" sheetId="8" r:id="rId4"/>
-    <sheet name="Soil Sample Management" sheetId="6" r:id="rId5"/>
-    <sheet name="H Calibration" sheetId="4" r:id="rId6"/>
-    <sheet name="incomplete 01-28-26 Soy-UD" sheetId="5" r:id="rId7"/>
+    <sheet name="DNA Samples for Sequencing" sheetId="9" r:id="rId4"/>
+    <sheet name="Soil Samples for Rutgers" sheetId="8" r:id="rId5"/>
+    <sheet name="Soil Sample Management" sheetId="6" r:id="rId6"/>
+    <sheet name="H Calibration" sheetId="4" r:id="rId7"/>
+    <sheet name="incomplete 01-28-26 Soy-UD" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="265">
   <si>
     <t>Soybean Undisturbed</t>
   </si>
@@ -611,9 +612,6 @@
     <t>WP may be wrong, number slipped mind (but I think it was -19.something)</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>FGF-FBW-15-1</t>
   </si>
   <si>
@@ -648,16 +646,210 @@
   </si>
   <si>
     <t>FGF-SUN-25-3</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Sample # (on Cap)</t>
+  </si>
+  <si>
+    <t>FGF-RM-20-1</t>
+  </si>
+  <si>
+    <t>FGF-RM-20-2</t>
+  </si>
+  <si>
+    <t>FGF-RM-20-3</t>
+  </si>
+  <si>
+    <t>FGF-SF-20-1</t>
+  </si>
+  <si>
+    <t>FGF-SF-20-2</t>
+  </si>
+  <si>
+    <t>FGF-SF-20-3</t>
+  </si>
+  <si>
+    <t>FGF-OR-20-1</t>
+  </si>
+  <si>
+    <t>FGF-OR-20-2</t>
+  </si>
+  <si>
+    <t>FGF-OR-20-3</t>
+  </si>
+  <si>
+    <t>FGF-SOD-20-1</t>
+  </si>
+  <si>
+    <t>FGF-SOD-20-2</t>
+  </si>
+  <si>
+    <t>FGF-SOD-20-3</t>
+  </si>
+  <si>
+    <t>MF-AS-20-1</t>
+  </si>
+  <si>
+    <t>MF-AS-20-2</t>
+  </si>
+  <si>
+    <t>MF-AS-20-3</t>
+  </si>
+  <si>
+    <t>FGF-BW-20-1</t>
+  </si>
+  <si>
+    <t>FGF-BW-20-2</t>
+  </si>
+  <si>
+    <t>FGF-BW-20-3</t>
+  </si>
+  <si>
+    <t>MF-CH-20-1</t>
+  </si>
+  <si>
+    <t>MF-CH-20-2</t>
+  </si>
+  <si>
+    <t>MF-CH-20-3</t>
+  </si>
+  <si>
+    <t>Soy-UD-15-3</t>
+  </si>
+  <si>
+    <t>Soy-UD-25-1</t>
+  </si>
+  <si>
+    <t>Soy-UD-25-2</t>
+  </si>
+  <si>
+    <t>Soy-UD-25-3</t>
+  </si>
+  <si>
+    <t>Soy-C-15-1</t>
+  </si>
+  <si>
+    <t>Soy-C-15-2</t>
+  </si>
+  <si>
+    <t>Soy-C-15-3</t>
+  </si>
+  <si>
+    <t>Soy-C-25-1</t>
+  </si>
+  <si>
+    <t>Soy-C-25-2</t>
+  </si>
+  <si>
+    <t>Soy-C-25-3</t>
+  </si>
+  <si>
+    <t>FGF-CO-20-1</t>
+  </si>
+  <si>
+    <t>FGF-CO-20-2</t>
+  </si>
+  <si>
+    <t>FGF-CO-20-3</t>
+  </si>
+  <si>
+    <t>FGF-CO-15-1</t>
+  </si>
+  <si>
+    <t>FGF-CO-15-2</t>
+  </si>
+  <si>
+    <t>FGF-CO-15-3</t>
+  </si>
+  <si>
+    <t>FGF-CO-25-1</t>
+  </si>
+  <si>
+    <t>FGF-CO-25-2</t>
+  </si>
+  <si>
+    <t>FGF-CO-25-3</t>
+  </si>
+  <si>
+    <t>Sample Name Underscores</t>
+  </si>
+  <si>
+    <t>Wrong name in nanodrop:</t>
+  </si>
+  <si>
+    <t>Labelled as second MF-CH-20-2</t>
+  </si>
+  <si>
+    <t>Labelled 25-1</t>
+  </si>
+  <si>
+    <t>Realized here I had not been wiping top mount of nanodrop</t>
+  </si>
+  <si>
+    <t>174.5 upon redo</t>
+  </si>
+  <si>
+    <t>2nd MF-20-2 is this one - got a replicate on accident</t>
+  </si>
+  <si>
+    <t>216.8 upon redo</t>
+  </si>
+  <si>
+    <t>63.2 Upon redo</t>
+  </si>
+  <si>
+    <t>133.9 redo</t>
+  </si>
+  <si>
+    <t>450.8 on redo</t>
+  </si>
+  <si>
+    <t>57.7 redo</t>
+  </si>
+  <si>
+    <t>287.7 redo</t>
+  </si>
+  <si>
+    <t>147.3 redo, 141.1 redo 2, 137.3 redo 3</t>
+  </si>
+  <si>
+    <t>234.5 redo</t>
+  </si>
+  <si>
+    <t>462.5 redo</t>
+  </si>
+  <si>
+    <t>758.3 upon redo, 596.4 redo again, 619.7 redo again</t>
+  </si>
+  <si>
+    <t>0;5014</t>
+  </si>
+  <si>
+    <t>739.2 redo, 1138.1 redo again, 641.4 redo again</t>
+  </si>
+  <si>
+    <t>554.5 redo, 553.1 redo again</t>
+  </si>
+  <si>
+    <t>*OLD* NanoDrop DNA conc (ng/uL)</t>
+  </si>
+  <si>
+    <t>Correct NanoDrop DNA Conc (ng/ul)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -708,7 +900,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -725,6 +917,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,10 +1993,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4433,7 +4623,7 @@
         <v>46050</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E43" si="0">_xlfn.DAYS(D4,C4)</f>
+        <f t="shared" ref="E4:E62" si="0">_xlfn.DAYS(D4,C4)</f>
         <v>14</v>
       </c>
       <c r="F4" s="2">
@@ -6443,16 +6633,44 @@
       <c r="C44" s="4">
         <v>46098</v>
       </c>
-      <c r="D44" s="4"/>
+      <c r="D44" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F44" s="2">
         <f>2.0083-0.002</f>
         <v>2.0063000000000004</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="M44" s="9"/>
-      <c r="N44" s="8"/>
+      <c r="G44" s="2">
+        <v>0.50339999999999996</v>
+      </c>
+      <c r="H44" s="3">
+        <v>-23.1</v>
+      </c>
+      <c r="I44" s="2">
+        <v>10.0167</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10.5594</v>
+      </c>
+      <c r="K44" s="2">
+        <v>10.5412</v>
+      </c>
+      <c r="L44" s="2">
+        <f t="shared" ref="L44:L61" si="3">(J44-K44)/(K44-I44)</f>
+        <v>3.4699714013346469E-2</v>
+      </c>
+      <c r="M44" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B44, Characterization!A:A, 0))*L44/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B44, Characterization!A:A, 0))*0.01)</f>
+        <v>9.9036138313546546E-2</v>
+      </c>
+      <c r="N44" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B44, Characterization!A:A, 0))*F44</f>
+        <v>8.0068814235591521E-2</v>
+      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
@@ -6464,13 +6682,44 @@
       <c r="C45" s="4">
         <v>46098</v>
       </c>
-      <c r="D45" s="4"/>
+      <c r="D45" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F45" s="2">
         <f>2.0048-0.0029</f>
         <v>2.0019</v>
       </c>
-      <c r="M45" s="9"/>
-      <c r="N45" s="8"/>
+      <c r="G45" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="3">
+        <v>-12.85</v>
+      </c>
+      <c r="I45" s="2">
+        <v>10.873699999999999</v>
+      </c>
+      <c r="J45" s="2">
+        <v>11.383599999999999</v>
+      </c>
+      <c r="K45" s="2">
+        <v>11.363</v>
+      </c>
+      <c r="L45" s="2">
+        <f t="shared" si="3"/>
+        <v>4.2100960555896072E-2</v>
+      </c>
+      <c r="M45" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B45, Characterization!A:A, 0))*L45/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B45, Characterization!A:A, 0))*0.01)</f>
+        <v>0.12015996878657788</v>
+      </c>
+      <c r="N45" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B45, Characterization!A:A, 0))*F45</f>
+        <v>7.9893215978782156E-2</v>
+      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
@@ -6482,13 +6731,44 @@
       <c r="C46" s="4">
         <v>46098</v>
       </c>
-      <c r="D46" s="4"/>
+      <c r="D46" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F46" s="2">
         <f>2.0052-0.0021</f>
         <v>2.0030999999999999</v>
       </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="8"/>
+      <c r="G46" s="2">
+        <v>0.5141</v>
+      </c>
+      <c r="H46" s="3">
+        <v>-23.88</v>
+      </c>
+      <c r="I46" s="2">
+        <v>10.099500000000001</v>
+      </c>
+      <c r="J46" s="2">
+        <v>10.6052</v>
+      </c>
+      <c r="K46" s="2">
+        <v>10.588900000000001</v>
+      </c>
+      <c r="L46" s="2">
+        <f t="shared" si="3"/>
+        <v>3.3306089088678631E-2</v>
+      </c>
+      <c r="M46" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B46, Characterization!A:A, 0))*L46/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B46, Characterization!A:A, 0))*0.01)</f>
+        <v>9.5058606085369562E-2</v>
+      </c>
+      <c r="N46" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B46, Characterization!A:A, 0))*F46</f>
+        <v>7.9941106412457427E-2</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
@@ -6500,13 +6780,44 @@
       <c r="C47" s="4">
         <v>46098</v>
       </c>
-      <c r="D47" s="4"/>
+      <c r="D47" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F47" s="2">
         <f>2.0041-0.0034</f>
         <v>2.0007000000000001</v>
       </c>
-      <c r="M47" s="9"/>
-      <c r="N47" s="8"/>
+      <c r="G47" s="2">
+        <v>0.49740000000000001</v>
+      </c>
+      <c r="H47" s="3">
+        <v>-5.24</v>
+      </c>
+      <c r="I47" s="2">
+        <v>10.8667</v>
+      </c>
+      <c r="J47" s="2">
+        <v>11.4329</v>
+      </c>
+      <c r="K47" s="2">
+        <v>11.402200000000001</v>
+      </c>
+      <c r="L47" s="2">
+        <f t="shared" si="3"/>
+        <v>5.7329598506068093E-2</v>
+      </c>
+      <c r="M47" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B47, Characterization!A:A, 0))*L47/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B47, Characterization!A:A, 0))*0.01)</f>
+        <v>0.16362388591800064</v>
+      </c>
+      <c r="N47" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B47, Characterization!A:A, 0))*F47</f>
+        <v>7.9845325545106885E-2</v>
+      </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
@@ -6518,13 +6829,44 @@
       <c r="C48" s="4">
         <v>46098</v>
       </c>
-      <c r="D48" s="4"/>
+      <c r="D48" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F48" s="2">
         <f>2.0013-0.0017</f>
         <v>1.9996</v>
       </c>
-      <c r="M48" s="9"/>
-      <c r="N48" s="8"/>
+      <c r="G48" s="2">
+        <v>0.50519999999999998</v>
+      </c>
+      <c r="H48" s="3">
+        <v>-5.61</v>
+      </c>
+      <c r="I48" s="2">
+        <v>10.1945</v>
+      </c>
+      <c r="J48" s="2">
+        <v>10.7476</v>
+      </c>
+      <c r="K48" s="2">
+        <v>10.716200000000001</v>
+      </c>
+      <c r="L48" s="2">
+        <f t="shared" si="3"/>
+        <v>6.01878474218892E-2</v>
+      </c>
+      <c r="M48" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B48, Characterization!A:A, 0))*L48/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B48, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17178158816456462</v>
+      </c>
+      <c r="N48" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B48, Characterization!A:A, 0))*F48</f>
+        <v>7.9801425980904533E-2</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
@@ -6536,17 +6878,48 @@
       <c r="C49" s="4">
         <v>46098</v>
       </c>
-      <c r="D49" s="4"/>
+      <c r="D49" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="F49" s="2">
         <f>2.0024-0.0027</f>
         <v>1.9997000000000003</v>
       </c>
-      <c r="M49" s="9"/>
-      <c r="N49" s="8"/>
+      <c r="G49" s="2">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="H49" s="3">
+        <v>-6.62</v>
+      </c>
+      <c r="I49" s="2">
+        <v>10.2639</v>
+      </c>
+      <c r="J49" s="2">
+        <v>10.7363</v>
+      </c>
+      <c r="K49" s="2">
+        <v>10.712300000000001</v>
+      </c>
+      <c r="L49" s="2">
+        <f t="shared" si="3"/>
+        <v>5.3523639607491229E-2</v>
+      </c>
+      <c r="M49" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B49, Characterization!A:A, 0))*L49/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B49, Characterization!A:A, 0))*0.01)</f>
+        <v>0.15276133322519878</v>
+      </c>
+      <c r="N49" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B49, Characterization!A:A, 0))*F49</f>
+        <v>7.9805416850377481E-2</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
         <v>164</v>
@@ -6554,17 +6927,48 @@
       <c r="C50" s="4">
         <v>46100</v>
       </c>
-      <c r="D50" s="4"/>
+      <c r="D50" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F50" s="2">
         <f>2.002-0.0013</f>
         <v>2.0006999999999997</v>
       </c>
-      <c r="M50" s="9"/>
-      <c r="N50" s="8"/>
+      <c r="G50" s="2">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="H50" s="3">
+        <v>-10.15</v>
+      </c>
+      <c r="I50" s="2">
+        <v>10.7189</v>
+      </c>
+      <c r="J50" s="2">
+        <v>11.2569</v>
+      </c>
+      <c r="K50" s="2">
+        <v>11.2318</v>
+      </c>
+      <c r="L50" s="2">
+        <f t="shared" si="3"/>
+        <v>4.8937414700721611E-2</v>
+      </c>
+      <c r="M50" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B50, Characterization!A:A, 0))*L50/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B50, Characterization!A:A, 0))*0.01)</f>
+        <v>0.11243371027490792</v>
+      </c>
+      <c r="N50" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B50, Characterization!A:A, 0))*F50</f>
+        <v>7.8653977889724017E-2</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" t="s">
         <v>164</v>
@@ -6572,17 +6976,48 @@
       <c r="C51" s="4">
         <v>46100</v>
       </c>
-      <c r="D51" s="4"/>
+      <c r="D51" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F51" s="2">
         <f>2.0021-0.0009</f>
         <v>2.0011999999999999</v>
       </c>
-      <c r="M51" s="9"/>
-      <c r="N51" s="8"/>
+      <c r="G51" s="2">
+        <v>0.49659999999999999</v>
+      </c>
+      <c r="H51" s="3">
+        <v>-8.5500000000000007</v>
+      </c>
+      <c r="I51" s="2">
+        <v>10.160600000000001</v>
+      </c>
+      <c r="J51" s="2">
+        <v>10.7181</v>
+      </c>
+      <c r="K51" s="2">
+        <v>10.695499999999999</v>
+      </c>
+      <c r="L51" s="2">
+        <f t="shared" si="3"/>
+        <v>4.2250888016452944E-2</v>
+      </c>
+      <c r="M51" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B51, Characterization!A:A, 0))*L51/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B51, Characterization!A:A, 0))*0.01)</f>
+        <v>9.7071415217800661E-2</v>
+      </c>
+      <c r="N51" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B51, Characterization!A:A, 0))*F51</f>
+        <v>7.8673634504381321E-2</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
         <v>164</v>
@@ -6590,17 +7025,48 @@
       <c r="C52" s="4">
         <v>46100</v>
       </c>
-      <c r="D52" s="4"/>
+      <c r="D52" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F52" s="2">
         <f>2.0036-0.0017</f>
         <v>2.0019</v>
       </c>
-      <c r="M52" s="9"/>
-      <c r="N52" s="8"/>
+      <c r="G52" s="2">
+        <v>0.505</v>
+      </c>
+      <c r="H52" s="3">
+        <v>-13.67</v>
+      </c>
+      <c r="I52" s="2">
+        <v>9.7448999999999995</v>
+      </c>
+      <c r="J52" s="2">
+        <v>10.3002</v>
+      </c>
+      <c r="K52" s="2">
+        <v>10.2784</v>
+      </c>
+      <c r="L52" s="2">
+        <f t="shared" si="3"/>
+        <v>4.0862230552953523E-2</v>
+      </c>
+      <c r="M52" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B52, Characterization!A:A, 0))*L52/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B52, Characterization!A:A, 0))*0.01)</f>
+        <v>9.3880974695410735E-2</v>
+      </c>
+      <c r="N52" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B52, Characterization!A:A, 0))*F52</f>
+        <v>7.8701153764901555E-2</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
         <v>164</v>
@@ -6608,17 +7074,48 @@
       <c r="C53" s="4">
         <v>46100</v>
       </c>
-      <c r="D53" s="4"/>
+      <c r="D53" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F53" s="2">
         <f>2.0085-0.0019</f>
         <v>2.0066000000000002</v>
       </c>
-      <c r="M53" s="9"/>
-      <c r="N53" s="8"/>
+      <c r="G53" s="2">
+        <v>0.50249999999999995</v>
+      </c>
+      <c r="H53" s="3">
+        <v>-1.51</v>
+      </c>
+      <c r="I53" s="2">
+        <v>10.650399999999999</v>
+      </c>
+      <c r="J53" s="2">
+        <v>11.274800000000001</v>
+      </c>
+      <c r="K53" s="2">
+        <v>11.228199999999999</v>
+      </c>
+      <c r="L53" s="2">
+        <f t="shared" si="3"/>
+        <v>8.0650744202148739E-2</v>
+      </c>
+      <c r="M53" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B53, Characterization!A:A, 0))*L53/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B53, Characterization!A:A, 0))*0.01)</f>
+        <v>0.18529508480443677</v>
+      </c>
+      <c r="N53" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B53, Characterization!A:A, 0))*F53</f>
+        <v>7.8885925942680193E-2</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
         <v>164</v>
@@ -6626,17 +7123,48 @@
       <c r="C54" s="4">
         <v>46100</v>
       </c>
-      <c r="D54" s="4"/>
+      <c r="D54" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F54" s="2">
         <f>2.0032-0.0025</f>
         <v>2.0007000000000001</v>
       </c>
-      <c r="M54" s="9"/>
-      <c r="N54" s="8"/>
+      <c r="G54" s="2">
+        <v>0.51490000000000002</v>
+      </c>
+      <c r="H54" s="3">
+        <v>-1.62</v>
+      </c>
+      <c r="I54" s="2">
+        <v>10.289199999999999</v>
+      </c>
+      <c r="J54" s="2">
+        <v>10.752800000000001</v>
+      </c>
+      <c r="K54" s="2">
+        <v>10.7179</v>
+      </c>
+      <c r="L54" s="2">
+        <f t="shared" si="3"/>
+        <v>8.1408910660135989E-2</v>
+      </c>
+      <c r="M54" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B54, Characterization!A:A, 0))*L54/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B54, Characterization!A:A, 0))*0.01)</f>
+        <v>0.18703697224166249</v>
+      </c>
+      <c r="N54" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B54, Characterization!A:A, 0))*F54</f>
+        <v>7.865397788972403E-2</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
         <v>164</v>
@@ -6644,85 +7172,335 @@
       <c r="C55" s="4">
         <v>46100</v>
       </c>
-      <c r="D55" s="4"/>
+      <c r="D55" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F55" s="2">
         <f>2.0021-0.0037</f>
         <v>1.9984</v>
       </c>
-      <c r="M55" s="9"/>
-      <c r="N55" s="8"/>
+      <c r="G55" s="2">
+        <v>0.503</v>
+      </c>
+      <c r="H55" s="3">
+        <v>-2.11</v>
+      </c>
+      <c r="I55" s="2">
+        <v>10.1212</v>
+      </c>
+      <c r="J55" s="2">
+        <v>10.7133</v>
+      </c>
+      <c r="K55" s="2">
+        <v>10.6708</v>
+      </c>
+      <c r="L55" s="2">
+        <f t="shared" si="3"/>
+        <v>7.7328966521107059E-2</v>
+      </c>
+      <c r="M55" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B55, Characterization!A:A, 0))*L55/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B55, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17766330058224353</v>
+      </c>
+      <c r="N55" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B55, Characterization!A:A, 0))*F55</f>
+        <v>7.856355746230044E-2</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="8"/>
+      <c r="C56" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D56" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F56" s="2">
+        <f>2.0024-0.0023</f>
+        <v>2.0001000000000002</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0.49709999999999999</v>
+      </c>
+      <c r="H56" s="3">
+        <v>-28.37</v>
+      </c>
+      <c r="I56" s="2">
+        <v>10.866300000000001</v>
+      </c>
+      <c r="J56" s="2">
+        <v>11.392099999999999</v>
+      </c>
+      <c r="K56" s="2">
+        <v>11.373100000000001</v>
+      </c>
+      <c r="L56" s="2">
+        <f t="shared" si="3"/>
+        <v>3.7490134175213782E-2</v>
+      </c>
+      <c r="M56" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B56, Characterization!A:A, 0))*L56/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B56, Characterization!A:A, 0))*0.01)</f>
+        <v>0.10795454545453606</v>
+      </c>
+      <c r="N56" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B56, Characterization!A:A, 0))*F56</f>
+        <v>8.1511950488862395E-2</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
         <v>162</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="8"/>
+      <c r="C57" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D57" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F57" s="2">
+        <f>2.0038-0.0042</f>
+        <v>1.9996</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0.49809999999999999</v>
+      </c>
+      <c r="H57" s="3">
+        <v>-40.17</v>
+      </c>
+      <c r="I57" s="2">
+        <v>10.8736</v>
+      </c>
+      <c r="J57" s="2">
+        <v>11.370699999999999</v>
+      </c>
+      <c r="K57" s="2">
+        <v>11.3551</v>
+      </c>
+      <c r="L57" s="2">
+        <f t="shared" si="3"/>
+        <v>3.2398753894079244E-2</v>
+      </c>
+      <c r="M57" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B57, Characterization!A:A, 0))*L57/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B57, Characterization!A:A, 0))*0.01)</f>
+        <v>9.3293684508632735E-2</v>
+      </c>
+      <c r="N57" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B57, Characterization!A:A, 0))*F57</f>
+        <v>8.1491573520088623E-2</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="8"/>
+      <c r="C58" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D58" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F58" s="2">
+        <f>2.0081-0.0025</f>
+        <v>2.0056000000000003</v>
+      </c>
+      <c r="H58" s="3">
+        <v>-43.07</v>
+      </c>
+      <c r="I58" s="2">
+        <v>10.099600000000001</v>
+      </c>
+      <c r="J58" s="2">
+        <v>10.6029</v>
+      </c>
+      <c r="K58" s="2">
+        <v>10.5863</v>
+      </c>
+      <c r="L58" s="2">
+        <f t="shared" si="3"/>
+        <v>3.4107252927882525E-2</v>
+      </c>
+      <c r="M58" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B58, Characterization!A:A, 0))*L58/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B58, Characterization!A:A, 0))*0.01)</f>
+        <v>9.8213385135516279E-2</v>
+      </c>
+      <c r="N58" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B58, Characterization!A:A, 0))*F58</f>
+        <v>8.1736097145373957E-2</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="8"/>
+      <c r="C59" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F59" s="2">
+        <f>2.0044-0.0019</f>
+        <v>2.0024999999999999</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0.51390000000000002</v>
+      </c>
+      <c r="H59" s="3">
+        <v>-5.77</v>
+      </c>
+      <c r="I59" s="2">
+        <v>10.0169</v>
+      </c>
+      <c r="J59" s="2">
+        <v>10.569599999999999</v>
+      </c>
+      <c r="K59" s="2">
+        <v>10.5375</v>
+      </c>
+      <c r="L59" s="2">
+        <f t="shared" si="3"/>
+        <v>6.1659623511332688E-2</v>
+      </c>
+      <c r="M59" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B59, Characterization!A:A, 0))*L59/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B59, Characterization!A:A, 0))*0.01)</f>
+        <v>0.17755168861104209</v>
+      </c>
+      <c r="N59" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B59, Characterization!A:A, 0))*F59</f>
+        <v>8.1609759938976525E-2</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="8"/>
+      <c r="C60" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D60" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F60" s="2">
+        <f>2.0056-0.003</f>
+        <v>2.0025999999999997</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H60" s="3">
+        <v>-5.12</v>
+      </c>
+      <c r="I60" s="2">
+        <v>10.1943</v>
+      </c>
+      <c r="J60" s="2">
+        <v>10.7667</v>
+      </c>
+      <c r="K60" s="2">
+        <v>10.734999999999999</v>
+      </c>
+      <c r="L60" s="2">
+        <f t="shared" si="3"/>
+        <v>5.8627704827077437E-2</v>
+      </c>
+      <c r="M60" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B60, Characterization!A:A, 0))*L60/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B60, Characterization!A:A, 0))*0.01)</f>
+        <v>0.16882114094524348</v>
+      </c>
+      <c r="N60" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B60, Characterization!A:A, 0))*F60</f>
+        <v>8.1613835332731269E-2</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>162</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="8"/>
+      <c r="C61" s="4">
+        <v>46101</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F61" s="2">
+        <f>2.0033-0.0025</f>
+        <v>2.0007999999999999</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0.50649999999999995</v>
+      </c>
+      <c r="H61" s="3">
+        <v>-6.76</v>
+      </c>
+      <c r="I61" s="2">
+        <v>10.203900000000001</v>
+      </c>
+      <c r="J61" s="2">
+        <v>10.795500000000001</v>
+      </c>
+      <c r="K61" s="2">
+        <v>10.7651</v>
+      </c>
+      <c r="L61" s="2">
+        <f t="shared" si="3"/>
+        <v>5.4169636493229208E-2</v>
+      </c>
+      <c r="M61" s="9">
+        <f>INDEX(Characterization!M:M, MATCH('Trial Metadata'!B61, Characterization!A:A, 0))*L61/(INDEX(Characterization!O:O, MATCH('Trial Metadata'!B61, Characterization!A:A, 0))*0.01)</f>
+        <v>0.15598393053845774</v>
+      </c>
+      <c r="N61" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B61, Characterization!A:A, 0))*F61</f>
+        <v>8.1540478245145681E-2</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -6735,10 +7513,15 @@
       <c r="C62" s="4">
         <v>46031</v>
       </c>
+      <c r="D62" s="4"/>
       <c r="F62" s="2">
         <f>2.0038-0.0083</f>
         <v>1.9955000000000001</v>
       </c>
+      <c r="N62" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B62, Characterization!A:A, 0))*F62</f>
+        <v>9.5923997443002049E-2</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
@@ -6751,10 +7534,15 @@
       <c r="C63" s="4">
         <v>46031</v>
       </c>
+      <c r="D63" s="4"/>
       <c r="F63" s="2">
         <f>2.0063-0.0145</f>
         <v>1.9918</v>
       </c>
+      <c r="N63" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B63, Characterization!A:A, 0))*F63</f>
+        <v>9.5746137863679026E-2</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
@@ -6767,12 +7555,17 @@
       <c r="C64" s="4">
         <v>46031</v>
       </c>
+      <c r="D64" s="4"/>
       <c r="F64" s="2">
         <f>2.0138-0.0145</f>
         <v>1.9992999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="N64" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B64, Characterization!A:A, 0))*F64</f>
+        <v>9.6106664037982459E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>57</v>
       </c>
@@ -6783,12 +7576,17 @@
       <c r="C65" s="4">
         <v>46031</v>
       </c>
+      <c r="D65" s="4"/>
       <c r="F65" s="2">
         <f>2.0277-0.0147</f>
         <v>2.0129999999999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="N65" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B65, Characterization!A:A, 0))*F65</f>
+        <v>9.676522518304341E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -6799,12 +7597,17 @@
       <c r="C66" s="4">
         <v>46031</v>
       </c>
+      <c r="D66" s="4"/>
       <c r="F66" s="2">
         <f>2.0169-0.0108</f>
         <v>2.0061</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="N66" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B66, Characterization!A:A, 0))*F66</f>
+        <v>9.6433541102684248E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -6815,9 +7618,14 @@
       <c r="C67" s="4">
         <v>46031</v>
       </c>
+      <c r="D67" s="4"/>
       <c r="F67" s="2">
         <f>2.0203-0.0114</f>
         <v>2.0089000000000001</v>
+      </c>
+      <c r="N67" s="8">
+        <f>INDEX(Characterization!S:S, MATCH('Trial Metadata'!B67, Characterization!A:A, 0))*F67</f>
+        <v>9.6568137541090879E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6828,6 +7636,1940 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB2F3F8-58E1-498C-8CE8-5AC6F1098C32}">
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="23.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" t="str">
+        <f>CONCATENATE(ROW(B2)-1,"-",TEXT(B2, "mm-dd-yyyy"),"-",C2)</f>
+        <v>1-07-18-2025-FGF-SF-20-1</v>
+      </c>
+      <c r="E2" t="str">
+        <f>SUBSTITUTE(D2,"-","_")</f>
+        <v>1_07_18_2025_FGF_SF_20_1</v>
+      </c>
+      <c r="F2" s="13">
+        <v>148.1</v>
+      </c>
+      <c r="G2" s="13">
+        <v>149</v>
+      </c>
+      <c r="H2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D66" si="0">CONCATENATE(ROW(B3)-1,"-",TEXT(B3, "mm-dd-yyyy"),"-",C3)</f>
+        <v>2-07-18-2025-FGF-SF-20-2</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E4" si="1">SUBSTITUTE(D3,"-","_")</f>
+        <v>2_07_18_2025_FGF_SF_20_2</v>
+      </c>
+      <c r="F3" s="13">
+        <v>132.69999999999999</v>
+      </c>
+      <c r="G3" s="13">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>3-07-18-2025-FGF-SF-20-3</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="1"/>
+        <v>3_07_18_2025_FGF_SF_20_3</v>
+      </c>
+      <c r="F4" s="13">
+        <v>171.9</v>
+      </c>
+      <c r="G4" s="13">
+        <v>171.6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>4-07-22-2025-FGF-RM-20-1</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" ref="E3:E66" si="2">SUBSTITUTE(D5,"-","_")</f>
+        <v>4_07_22_2025_FGF_RM_20_1</v>
+      </c>
+      <c r="F5" s="13">
+        <v>287.7</v>
+      </c>
+      <c r="G5" s="13">
+        <v>276</v>
+      </c>
+      <c r="I5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>5-07-22-2025-FGF-RM-20-2</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="2"/>
+        <v>5_07_22_2025_FGF_RM_20_2</v>
+      </c>
+      <c r="F6" s="13">
+        <v>280.7</v>
+      </c>
+      <c r="G6" s="13">
+        <v>458.2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>6-07-22-2025-FGF-RM-20-3</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="2"/>
+        <v>6_07_22_2025_FGF_RM_20_3</v>
+      </c>
+      <c r="F7" s="13">
+        <v>271.10000000000002</v>
+      </c>
+      <c r="G7" s="13">
+        <v>323.7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I7" t="s">
+        <v>244</v>
+      </c>
+      <c r="J7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>7-07-18-2025-FGF-CO-20-1</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="2"/>
+        <v>7_07_18_2025_FGF_CO_20_1</v>
+      </c>
+      <c r="F8" s="13">
+        <v>245.2</v>
+      </c>
+      <c r="G8" s="13">
+        <v>540.9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>8-07-18-2025-FGF-CO-20-2</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="2"/>
+        <v>8_07_18_2025_FGF_CO_20_2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>201.9</v>
+      </c>
+      <c r="G9" s="13">
+        <v>180.2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12">
+        <v>45856</v>
+      </c>
+      <c r="C10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>9-07-18-2025-FGF-CO-20-3</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="2"/>
+        <v>9_07_18_2025_FGF_CO_20_3</v>
+      </c>
+      <c r="F10" s="13">
+        <v>182.4</v>
+      </c>
+      <c r="G10" s="13">
+        <v>198.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>10-07-22-2025-FGF-OR-20-1</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="2"/>
+        <v>10_07_22_2025_FGF_OR_20_1</v>
+      </c>
+      <c r="F11" s="13">
+        <v>197</v>
+      </c>
+      <c r="G11" s="13">
+        <v>186.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>11-07-22-2025-FGF-OR-20-2</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="2"/>
+        <v>11_07_22_2025_FGF_OR_20_2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>172.2</v>
+      </c>
+      <c r="G12" s="13">
+        <v>212.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12">
+        <v>45860</v>
+      </c>
+      <c r="C13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>12-07-22-2025-FGF-OR-20-3</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="2"/>
+        <v>12_07_22_2025_FGF_OR_20_3</v>
+      </c>
+      <c r="F13" s="13">
+        <v>246.1</v>
+      </c>
+      <c r="G13" s="13">
+        <v>230.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>13-07-24-2025-FGF-SOD-20-1</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="2"/>
+        <v>13_07_24_2025_FGF_SOD_20_1</v>
+      </c>
+      <c r="F14" s="13">
+        <v>619.79999999999995</v>
+      </c>
+      <c r="G14" s="13">
+        <v>1009.2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C15" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>14-07-24-2025-FGF-SOD-20-2</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="2"/>
+        <v>14_07_24_2025_FGF_SOD_20_2</v>
+      </c>
+      <c r="F15" s="13">
+        <v>671.8</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1344.7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>15-07-24-2025-FGF-SOD-20-3</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="2"/>
+        <v>15_07_24_2025_FGF_SOD_20_3</v>
+      </c>
+      <c r="F16" s="13">
+        <v>580.20000000000005</v>
+      </c>
+      <c r="G16" s="13">
+        <v>1153.9000000000001</v>
+      </c>
+      <c r="H16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>16-07-30-2026-MF-AS-20-1</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="2"/>
+        <v>16_07_30_2026_MF_AS_20_1</v>
+      </c>
+      <c r="F17" s="13">
+        <v>97.8</v>
+      </c>
+      <c r="G17" s="13">
+        <v>96.6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>17-07-30-2026-MF-AS-20-2</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="2"/>
+        <v>17_07_30_2026_MF_AS_20_2</v>
+      </c>
+      <c r="F18" s="13">
+        <v>143</v>
+      </c>
+      <c r="G18" s="13">
+        <v>275.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>18-07-30-2026-MF-AS-20-3</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="2"/>
+        <v>18_07_30_2026_MF_AS_20_3</v>
+      </c>
+      <c r="F19" s="13">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="G19" s="13">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="H19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>19-07-24-2025-FGF-BW-20-1</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="2"/>
+        <v>19_07_24_2025_FGF_BW_20_1</v>
+      </c>
+      <c r="F20" s="13">
+        <v>207.9</v>
+      </c>
+      <c r="G20" s="13">
+        <v>284.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>20-07-24-2025-FGF-BW-20-2</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="2"/>
+        <v>20_07_24_2025_FGF_BW_20_2</v>
+      </c>
+      <c r="F21" s="13">
+        <v>263.60000000000002</v>
+      </c>
+      <c r="G21" s="13">
+        <v>561.20000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
+        <v>45862</v>
+      </c>
+      <c r="C22" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>21-07-24-2025-FGF-BW-20-3</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="2"/>
+        <v>21_07_24_2025_FGF_BW_20_3</v>
+      </c>
+      <c r="F22" s="13">
+        <v>226.5</v>
+      </c>
+      <c r="G22" s="13">
+        <v>239.7</v>
+      </c>
+      <c r="H22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C23" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>22-07-30-2026-MF-CH-20-1</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="2"/>
+        <v>22_07_30_2026_MF_CH_20_1</v>
+      </c>
+      <c r="F23" s="13">
+        <v>62.1</v>
+      </c>
+      <c r="G23" s="13">
+        <v>59.7</v>
+      </c>
+      <c r="H23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C24" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>23-07-30-2026-MF-CH-20-2</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="2"/>
+        <v>23_07_30_2026_MF_CH_20_2</v>
+      </c>
+      <c r="F24" s="13">
+        <v>101.7</v>
+      </c>
+      <c r="G24" s="13">
+        <v>140.19999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="12">
+        <v>46233</v>
+      </c>
+      <c r="C25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>24-07-30-2026-MF-CH-20-3</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="2"/>
+        <v>24_07_30_2026_MF_CH_20_3</v>
+      </c>
+      <c r="F25" s="13">
+        <v>91.2</v>
+      </c>
+      <c r="G25" s="13">
+        <v>94.2</v>
+      </c>
+      <c r="H25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>25-03-09-2026-Soy-UD-15-1</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="2"/>
+        <v>25_03_09_2026_Soy_UD_15_1</v>
+      </c>
+      <c r="F26" s="13">
+        <v>447.4</v>
+      </c>
+      <c r="G26" s="13">
+        <v>637.29999999999995</v>
+      </c>
+      <c r="H26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>26-03-09-2026-Soy-UD-15-2</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="2"/>
+        <v>26_03_09_2026_Soy_UD_15_2</v>
+      </c>
+      <c r="F27" s="13">
+        <v>574.70000000000005</v>
+      </c>
+      <c r="G27" s="13">
+        <v>564.20000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-09-2026-Soy-UD-15-3</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="2"/>
+        <v>27_03_09_2026_Soy_UD_15_3</v>
+      </c>
+      <c r="F28" s="13">
+        <v>453.1</v>
+      </c>
+      <c r="G28" s="13">
+        <v>967.6</v>
+      </c>
+      <c r="H28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C29" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>28-03-09-2026-Soy-UD-25-1</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="2"/>
+        <v>28_03_09_2026_Soy_UD_25_1</v>
+      </c>
+      <c r="F29" s="13">
+        <v>461.8</v>
+      </c>
+      <c r="G29" s="13">
+        <v>730.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C30" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>29-03-09-2026-Soy-UD-25-2</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="2"/>
+        <v>29_03_09_2026_Soy_UD_25_2</v>
+      </c>
+      <c r="F30" s="13">
+        <v>348.2</v>
+      </c>
+      <c r="G30" s="13">
+        <v>292</v>
+      </c>
+      <c r="H30" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C31" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v>30-03-09-2026-Soy-UD-25-3</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="2"/>
+        <v>30_03_09_2026_Soy_UD_25_3</v>
+      </c>
+      <c r="F31" s="13">
+        <v>445.5</v>
+      </c>
+      <c r="G31" s="13">
+        <v>944.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v>31-03-10-2026-Soy-C-15-1</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="2"/>
+        <v>31_03_10_2026_Soy_C_15_1</v>
+      </c>
+      <c r="F32" s="13">
+        <v>133.5</v>
+      </c>
+      <c r="G32" s="13">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="0"/>
+        <v>32-03-10-2026-Soy-C-15-2</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="2"/>
+        <v>32_03_10_2026_Soy_C_15_2</v>
+      </c>
+      <c r="F33" s="13">
+        <v>207.6</v>
+      </c>
+      <c r="G33" s="13">
+        <v>245.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C34" t="s">
+        <v>230</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v>33-03-10-2026-Soy-C-15-3</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="2"/>
+        <v>33_03_10_2026_Soy_C_15_3</v>
+      </c>
+      <c r="F34" s="13">
+        <v>169.4</v>
+      </c>
+      <c r="G34" s="13">
+        <v>288.10000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C35" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v>34-03-10-2026-Soy-C-25-1</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="2"/>
+        <v>34_03_10_2026_Soy_C_25_1</v>
+      </c>
+      <c r="F35" s="13">
+        <v>122.5</v>
+      </c>
+      <c r="G35" s="13">
+        <v>108.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C36" t="s">
+        <v>232</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v>35-03-10-2026-Soy-C-25-2</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="2"/>
+        <v>35_03_10_2026_Soy_C_25_2</v>
+      </c>
+      <c r="F36" s="13">
+        <v>173.4</v>
+      </c>
+      <c r="G36" s="13">
+        <v>452.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v>36-03-10-2026-Soy-C-25-3</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="2"/>
+        <v>36_03_10_2026_Soy_C_25_3</v>
+      </c>
+      <c r="F37" s="13">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="G37" s="13">
+        <v>150.9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v>37-03-14-2026-FGF-OR-15-1</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="2"/>
+        <v>37_03_14_2026_FGF_OR_15_1</v>
+      </c>
+      <c r="F38" s="13">
+        <v>274.89999999999998</v>
+      </c>
+      <c r="G38" s="13">
+        <v>337.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C39" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v>38-03-14-2026-FGF-OR-15-2</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="2"/>
+        <v>38_03_14_2026_FGF_OR_15_2</v>
+      </c>
+      <c r="F39" s="13">
+        <v>245.5</v>
+      </c>
+      <c r="G39" s="13">
+        <v>314.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C40" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>39-03-14-2026-FGF-OR-15-3</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="2"/>
+        <v>39_03_14_2026_FGF_OR_15_3</v>
+      </c>
+      <c r="F40" s="13">
+        <v>192.7</v>
+      </c>
+      <c r="G40" s="13">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="0"/>
+        <v>40-03-14-2026-FGF-OR-25-1</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="2"/>
+        <v>40_03_14_2026_FGF_OR_25_1</v>
+      </c>
+      <c r="F41" s="13">
+        <v>225.5</v>
+      </c>
+      <c r="G41" s="13">
+        <v>729.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C42" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="0"/>
+        <v>41-03-14-2026-FGF-OR-25-2</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="2"/>
+        <v>41_03_14_2026_FGF_OR_25_2</v>
+      </c>
+      <c r="F42" s="13">
+        <v>258.60000000000002</v>
+      </c>
+      <c r="G42" s="13">
+        <v>416.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="12">
+        <v>46095</v>
+      </c>
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="0"/>
+        <v>42-03-14-2026-FGF-OR-25-3</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="2"/>
+        <v>42_03_14_2026_FGF_OR_25_3</v>
+      </c>
+      <c r="F43" s="13">
+        <v>237.4</v>
+      </c>
+      <c r="G43" s="13">
+        <v>171.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="0"/>
+        <v>43-03-15-2026-FGF-RO-15-1</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="2"/>
+        <v>43_03_15_2026_FGF_RO_15_1</v>
+      </c>
+      <c r="F44" s="13">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="G44" s="13">
+        <v>141.19999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C45" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="0"/>
+        <v>44-03-15-2026-FGF-RO-15-2</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="2"/>
+        <v>44_03_15_2026_FGF_RO_15_2</v>
+      </c>
+      <c r="F45" s="13">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="G45" s="13">
+        <v>139.30000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="0"/>
+        <v>45-03-15-2026-FGF-RO-15-3</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="2"/>
+        <v>45_03_15_2026_FGF_RO_15_3</v>
+      </c>
+      <c r="F46" s="13">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="G46" s="13">
+        <v>176.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C47" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v>46-03-15-2026-FGF-RO-25-1</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="2"/>
+        <v>46_03_15_2026_FGF_RO_25_1</v>
+      </c>
+      <c r="F47" s="13">
+        <v>223.8</v>
+      </c>
+      <c r="G47" s="13">
+        <v>293.39999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="0"/>
+        <v>47-03-15-2026-FGF-RO-25-2</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="2"/>
+        <v>47_03_15_2026_FGF_RO_25_2</v>
+      </c>
+      <c r="F48" s="13">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="G48" s="13">
+        <v>146.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="12">
+        <v>46096</v>
+      </c>
+      <c r="C49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="0"/>
+        <v>48-03-15-2026-FGF-RO-25-3</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="2"/>
+        <v>48_03_15_2026_FGF_RO_25_3</v>
+      </c>
+      <c r="F49" s="13">
+        <v>250.2</v>
+      </c>
+      <c r="G49" s="13">
+        <v>204.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C50" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="0"/>
+        <v>49-03-18-2026-FGF-SOD-15-1</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="2"/>
+        <v>49_03_18_2026_FGF_SOD_15_1</v>
+      </c>
+      <c r="F50" s="13">
+        <v>483.1</v>
+      </c>
+      <c r="G50" s="13">
+        <v>412.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C51" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="0"/>
+        <v>50-03-18-2026-FGF-SOD-15-2</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="2"/>
+        <v>50_03_18_2026_FGF_SOD_15_2</v>
+      </c>
+      <c r="F51" s="13">
+        <v>496.8</v>
+      </c>
+      <c r="G51" s="13">
+        <v>590.79999999999995</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="0"/>
+        <v>51-03-18-2026-FGF-SOD-15-3</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="2"/>
+        <v>51_03_18_2026_FGF_SOD_15_3</v>
+      </c>
+      <c r="F52" s="13">
+        <v>478</v>
+      </c>
+      <c r="G52" s="13">
+        <v>470.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v>52-03-18-2026-FGF-SOD-25-1</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="2"/>
+        <v>52_03_18_2026_FGF_SOD_25_1</v>
+      </c>
+      <c r="F53" s="13">
+        <v>494.6</v>
+      </c>
+      <c r="G53" s="13">
+        <v>563.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C54" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="0"/>
+        <v>53-03-18-2026-FGF-SOD-25-2</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="2"/>
+        <v>53_03_18_2026_FGF_SOD_25_2</v>
+      </c>
+      <c r="F54" s="13">
+        <v>506</v>
+      </c>
+      <c r="G54" s="13">
+        <v>517.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C55" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="0"/>
+        <v>54-03-18-2026-FGF-SOD-25-3</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="2"/>
+        <v>54_03_18_2026_FGF_SOD_25_3</v>
+      </c>
+      <c r="F55" s="13">
+        <v>460.1</v>
+      </c>
+      <c r="G55" s="13">
+        <v>466.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C56" t="s">
+        <v>237</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="0"/>
+        <v>55-03-22-2026-FGF-CO-15-1</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="2"/>
+        <v>55_03_22_2026_FGF_CO_15_1</v>
+      </c>
+      <c r="F56" s="13">
+        <v>248.6</v>
+      </c>
+      <c r="G56" s="13">
+        <v>238.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="0"/>
+        <v>56-03-22-2026-FGF-CO-15-2</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="2"/>
+        <v>56_03_22_2026_FGF_CO_15_2</v>
+      </c>
+      <c r="F57" s="13">
+        <v>213.7</v>
+      </c>
+      <c r="G57" s="13">
+        <v>197.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C58" t="s">
+        <v>239</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="0"/>
+        <v>57-03-22-2026-FGF-CO-15-3</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="2"/>
+        <v>57_03_22_2026_FGF_CO_15_3</v>
+      </c>
+      <c r="F58" s="13">
+        <v>178.1</v>
+      </c>
+      <c r="G58" s="13">
+        <v>168.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C59" t="s">
+        <v>240</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="0"/>
+        <v>58-03-22-2026-FGF-CO-25-1</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="2"/>
+        <v>58_03_22_2026_FGF_CO_25_1</v>
+      </c>
+      <c r="F59" s="13">
+        <v>275.5</v>
+      </c>
+      <c r="G59" s="13">
+        <v>294.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C60" t="s">
+        <v>241</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="0"/>
+        <v>59-03-22-2026-FGF-CO-25-2</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="2"/>
+        <v>59_03_22_2026_FGF_CO_25_2</v>
+      </c>
+      <c r="F60" s="13">
+        <v>183.3</v>
+      </c>
+      <c r="G60" s="13">
+        <v>174.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="12">
+        <v>46103</v>
+      </c>
+      <c r="C61" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="0"/>
+        <v>60-03-22-2026-FGF-CO-25-3</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="2"/>
+        <v>60_03_22_2026_FGF_CO_25_3</v>
+      </c>
+      <c r="F61" s="13">
+        <v>248.5</v>
+      </c>
+      <c r="G61" s="13">
+        <v>263.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="0"/>
+        <v>61-03-25-2026-FGF-FBW-15-1</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="2"/>
+        <v>61_03_25_2026_FGF_FBW_15_1</v>
+      </c>
+      <c r="F62" s="13">
+        <v>284</v>
+      </c>
+      <c r="G62" s="13">
+        <v>277.39999999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C63" t="s">
+        <v>190</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="0"/>
+        <v>62-03-25-2026-FGF-FBW-15-2</v>
+      </c>
+      <c r="E63" t="str">
+        <f t="shared" si="2"/>
+        <v>62_03_25_2026_FGF_FBW_15_2</v>
+      </c>
+      <c r="F63" s="13">
+        <v>286.60000000000002</v>
+      </c>
+      <c r="G63" s="13">
+        <v>238.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="0"/>
+        <v>63-03-25-2026-FGF-FBW-15-3</v>
+      </c>
+      <c r="E64" t="str">
+        <f t="shared" si="2"/>
+        <v>63_03_25_2026_FGF_FBW_15_3</v>
+      </c>
+      <c r="F64" s="13">
+        <v>195.9</v>
+      </c>
+      <c r="G64" s="13">
+        <v>184.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C65" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="0"/>
+        <v>64-03-25-2026-FGF-FBW-25-1</v>
+      </c>
+      <c r="E65" t="str">
+        <f t="shared" si="2"/>
+        <v>64_03_25_2026_FGF_FBW_25_1</v>
+      </c>
+      <c r="F65" s="13">
+        <v>175.7</v>
+      </c>
+      <c r="G65" s="13">
+        <v>170.7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C66" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="0"/>
+        <v>65-03-25-2026-FGF-FBW-25-2</v>
+      </c>
+      <c r="E66" t="str">
+        <f t="shared" si="2"/>
+        <v>65_03_25_2026_FGF_FBW_25_2</v>
+      </c>
+      <c r="F66" s="13">
+        <v>112.4</v>
+      </c>
+      <c r="G66" s="13">
+        <v>115.6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" ref="D67:D73" si="3">CONCATENATE(ROW(B67)-1,"-",TEXT(B67, "mm-dd-yyyy"),"-",C67)</f>
+        <v>66-03-25-2026-FGF-FBW-25-3</v>
+      </c>
+      <c r="E67" t="str">
+        <f t="shared" ref="E67:E73" si="4">SUBSTITUTE(D67,"-","_")</f>
+        <v>66_03_25_2026_FGF_FBW_25_3</v>
+      </c>
+      <c r="F67" s="13">
+        <v>187</v>
+      </c>
+      <c r="G67" s="13">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C68" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="3"/>
+        <v>67-03-26-2026-FGF-SUN-15-1</v>
+      </c>
+      <c r="E68" t="str">
+        <f t="shared" si="4"/>
+        <v>67_03_26_2026_FGF_SUN_15_1</v>
+      </c>
+      <c r="F68" s="13">
+        <v>135.69999999999999</v>
+      </c>
+      <c r="G68" s="13">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C69" t="s">
+        <v>196</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="3"/>
+        <v>68-03-26-2026-FGF-SUN-15-2</v>
+      </c>
+      <c r="E69" t="str">
+        <f t="shared" si="4"/>
+        <v>68_03_26_2026_FGF_SUN_15_2</v>
+      </c>
+      <c r="F69" s="13">
+        <v>126.2</v>
+      </c>
+      <c r="G69" s="13">
+        <v>112.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="3"/>
+        <v>69-03-26-2026-FGF-SUN-15-3</v>
+      </c>
+      <c r="E70" t="str">
+        <f t="shared" si="4"/>
+        <v>69_03_26_2026_FGF_SUN_15_3</v>
+      </c>
+      <c r="F70" s="13">
+        <v>107.4</v>
+      </c>
+      <c r="G70" s="13">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C71" t="s">
+        <v>198</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="3"/>
+        <v>70-03-26-2026-FGF-SUN-25-1</v>
+      </c>
+      <c r="E71" t="str">
+        <f t="shared" si="4"/>
+        <v>70_03_26_2026_FGF_SUN_25_1</v>
+      </c>
+      <c r="F71" s="13">
+        <v>159.80000000000001</v>
+      </c>
+      <c r="G71" s="13">
+        <v>149.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C72" t="s">
+        <v>199</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="3"/>
+        <v>71-03-26-2026-FGF-SUN-25-2</v>
+      </c>
+      <c r="E72" t="str">
+        <f t="shared" si="4"/>
+        <v>71_03_26_2026_FGF_SUN_25_2</v>
+      </c>
+      <c r="F72" s="13">
+        <v>140.5</v>
+      </c>
+      <c r="G72" s="13">
+        <v>129.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C73" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="3"/>
+        <v>72-03-26-2026-FGF-SUN-25-3</v>
+      </c>
+      <c r="E73" t="str">
+        <f t="shared" si="4"/>
+        <v>72_03_26_2026_FGF_SUN_25_3</v>
+      </c>
+      <c r="F73" s="13">
+        <v>189.8</v>
+      </c>
+      <c r="G73" s="13">
+        <v>176.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCD1671-150A-431B-9802-17D2A2E7407A}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7255,7 +9997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F465DB-3416-4852-B573-96C6ABA2B1A8}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7591,7 +10333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF4ED8B-9D6A-4DCD-8C9F-6E04025006A7}">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7881,7 +10623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD63824-F95F-4A24-9AAE-5CBB9DC71786}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
